--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/14,09,26 Останкино КИ и ЗПФ/дв 14,09,26 лгрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/09,26/14,09,26 Останкино КИ и ЗПФ/дв 14,09,26 лгрсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\09,26\14,09,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195776F1-4007-4526-AF55-5EC4C4E0AC97}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D5F9525-AE9C-44EA-AA0D-84472A63E65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AJ$104</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -685,7 +677,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -696,7 +688,6 @@
     <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -710,9 +701,7 @@
     <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -732,7 +721,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -5467,23 +5456,24 @@
   <dimension ref="A1:AY496"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60" style="10" customWidth="1"/>
-    <col min="2" max="2" width="3" style="10" customWidth="1"/>
-    <col min="3" max="4" width="6" style="10" customWidth="1"/>
-    <col min="5" max="6" width="7" style="10" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="3" customWidth="1"/>
+    <col min="3" max="4" width="6" customWidth="1"/>
+    <col min="5" max="6" width="7" customWidth="1"/>
     <col min="7" max="7" width="5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="5" style="10" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="1" style="10" customWidth="1"/>
-    <col min="11" max="12" width="7" style="10" customWidth="1"/>
-    <col min="13" max="14" width="0.42578125" style="10" customWidth="1"/>
-    <col min="15" max="20" width="7" style="10" customWidth="1"/>
-    <col min="21" max="22" width="7" style="25" customWidth="1"/>
-    <col min="23" max="24" width="5" style="10" customWidth="1"/>
-    <col min="25" max="34" width="6" style="10" customWidth="1"/>
-    <col min="35" max="35" width="44.140625" style="10" customWidth="1"/>
-    <col min="36" max="36" width="7" style="10" customWidth="1"/>
-    <col min="37" max="51" width="3" style="10" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" customWidth="1"/>
+    <col min="10" max="10" width="1" customWidth="1"/>
+    <col min="11" max="12" width="7" customWidth="1"/>
+    <col min="13" max="14" width="0.42578125" customWidth="1"/>
+    <col min="15" max="20" width="7" customWidth="1"/>
+    <col min="21" max="22" width="7" style="23" customWidth="1"/>
+    <col min="23" max="24" width="5" customWidth="1"/>
+    <col min="25" max="34" width="6" customWidth="1"/>
+    <col min="35" max="35" width="44.140625" customWidth="1"/>
+    <col min="36" max="36" width="7" customWidth="1"/>
+    <col min="37" max="37" width="5.7109375" customWidth="1"/>
+    <col min="38" max="51" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.25">
@@ -5911,7 +5901,10 @@
         <f>SUM(AJ6:AJ496)</f>
         <v>15048.739999999998</v>
       </c>
-      <c r="AK5" s="6"/>
+      <c r="AK5" s="3">
+        <f>SUM(AK6:AK496)</f>
+        <v>1750.5678000000007</v>
+      </c>
       <c r="AL5" s="6"/>
       <c r="AM5" s="6"/>
       <c r="AN5" s="6"/>
@@ -5978,11 +5971,11 @@
       <c r="T6" s="4">
         <v>50</v>
       </c>
-      <c r="U6" s="24">
+      <c r="U6" s="6">
         <f>VLOOKUP(A6,[1]Sheet!$A:$T,20,0)</f>
         <v>70</v>
       </c>
-      <c r="V6" s="24"/>
+      <c r="V6" s="6"/>
       <c r="W6" s="6">
         <f>(F6+O6+P6+Q6+T6)/R6</f>
         <v>38.336144763073143</v>
@@ -6028,7 +6021,10 @@
         <f>G6*T6</f>
         <v>50</v>
       </c>
-      <c r="AK6" s="6"/>
+      <c r="AK6" s="6">
+        <f>R6*G6</f>
+        <v>1.3042</v>
+      </c>
       <c r="AL6" s="6"/>
       <c r="AM6" s="6"/>
       <c r="AN6" s="6"/>
@@ -6099,8 +6095,8 @@
         <f t="shared" ref="T7:T66" si="5">ROUND(S7,0)</f>
         <v>235</v>
       </c>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
       <c r="W7" s="6">
         <f t="shared" ref="W7:W70" si="6">(F7+O7+P7+Q7+T7)/R7</f>
         <v>13.993288590604026</v>
@@ -6144,7 +6140,10 @@
         <f t="shared" ref="AJ7:AJ70" si="7">G7*T7</f>
         <v>94</v>
       </c>
-      <c r="AK7" s="6"/>
+      <c r="AK7" s="6">
+        <f t="shared" ref="AK7:AK70" si="8">R7*G7</f>
+        <v>11.920000000000002</v>
+      </c>
       <c r="AL7" s="6"/>
       <c r="AM7" s="6"/>
       <c r="AN7" s="6"/>
@@ -6212,11 +6211,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U8" s="24">
+      <c r="U8" s="6">
         <f>VLOOKUP(A8,[1]Sheet!$A:$T,20,0)</f>
         <v>90</v>
       </c>
-      <c r="V8" s="24"/>
+      <c r="V8" s="6"/>
       <c r="W8" s="6">
         <f t="shared" si="6"/>
         <v>21.98380723638336</v>
@@ -6255,14 +6254,17 @@
       <c r="AH8" s="6">
         <v>1.478</v>
       </c>
-      <c r="AI8" s="15" t="s">
+      <c r="AI8" s="14" t="s">
         <v>47</v>
       </c>
       <c r="AJ8" s="6">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK8" s="6"/>
+      <c r="AK8" s="6">
+        <f t="shared" si="8"/>
+        <v>2.5813999999999999</v>
+      </c>
       <c r="AL8" s="6"/>
       <c r="AM8" s="6"/>
       <c r="AN8" s="6"/>
@@ -6326,17 +6328,17 @@
         <v>14.6</v>
       </c>
       <c r="S9" s="4">
-        <f t="shared" ref="S9:S35" si="8">15*R9-Q9-P9-O9-F9</f>
+        <f t="shared" ref="S9:S35" si="9">15*R9-Q9-P9-O9-F9</f>
         <v>86</v>
       </c>
       <c r="T9" s="4">
         <v>150</v>
       </c>
-      <c r="U9" s="24">
+      <c r="U9" s="6">
         <f>VLOOKUP(A9,[1]Sheet!$A:$T,20,0)</f>
         <v>300</v>
       </c>
-      <c r="V9" s="24"/>
+      <c r="V9" s="6"/>
       <c r="W9" s="6">
         <f t="shared" si="6"/>
         <v>19.383561643835616</v>
@@ -6382,7 +6384,10 @@
         <f t="shared" si="7"/>
         <v>37.5</v>
       </c>
-      <c r="AK9" s="6"/>
+      <c r="AK9" s="6">
+        <f t="shared" si="8"/>
+        <v>3.65</v>
+      </c>
       <c r="AL9" s="6"/>
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
@@ -6446,15 +6451,15 @@
         <v>163.08620000000002</v>
       </c>
       <c r="S10" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1022.6860000000001</v>
       </c>
       <c r="T10" s="4">
         <f t="shared" si="5"/>
         <v>1023</v>
       </c>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
       <c r="W10" s="6">
         <f t="shared" si="6"/>
         <v>15.001925362170432</v>
@@ -6498,7 +6503,10 @@
         <f t="shared" si="7"/>
         <v>1023</v>
       </c>
-      <c r="AK10" s="6"/>
+      <c r="AK10" s="6">
+        <f t="shared" si="8"/>
+        <v>163.08620000000002</v>
+      </c>
       <c r="AL10" s="6"/>
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
@@ -6564,11 +6572,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U11" s="24">
+      <c r="U11" s="6">
         <f>VLOOKUP(A11,[1]Sheet!$A:$T,20,0)</f>
         <v>20</v>
       </c>
-      <c r="V11" s="24"/>
+      <c r="V11" s="6"/>
       <c r="W11" s="6">
         <f t="shared" si="6"/>
         <v>28.5681049069374</v>
@@ -6607,14 +6615,17 @@
       <c r="AH11" s="6">
         <v>5.2065999999999999</v>
       </c>
-      <c r="AI11" s="15" t="s">
+      <c r="AI11" s="14" t="s">
         <v>155</v>
       </c>
       <c r="AJ11" s="6">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="6"/>
+      <c r="AK11" s="6">
+        <f t="shared" si="8"/>
+        <v>3.3095999999999997</v>
+      </c>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
       <c r="AN11" s="6"/>
@@ -6676,17 +6687,17 @@
         <v>48.733199999999997</v>
       </c>
       <c r="S12" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>276.46499999999992</v>
       </c>
       <c r="T12" s="4">
         <v>450</v>
       </c>
-      <c r="U12" s="24">
+      <c r="U12" s="6">
         <f>VLOOKUP(A12,[1]Sheet!$A:$T,20,0)</f>
         <v>500</v>
       </c>
-      <c r="V12" s="24"/>
+      <c r="V12" s="6"/>
       <c r="W12" s="6">
         <f t="shared" si="6"/>
         <v>18.56091945531999</v>
@@ -6732,7 +6743,10 @@
         <f t="shared" si="7"/>
         <v>450</v>
       </c>
-      <c r="AK12" s="6"/>
+      <c r="AK12" s="6">
+        <f t="shared" si="8"/>
+        <v>48.733199999999997</v>
+      </c>
       <c r="AL12" s="6"/>
       <c r="AM12" s="6"/>
       <c r="AN12" s="6"/>
@@ -6796,17 +6810,17 @@
         <v>60.669000000000004</v>
       </c>
       <c r="S13" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>338.58300000000008</v>
       </c>
       <c r="T13" s="4">
         <v>600</v>
       </c>
-      <c r="U13" s="24">
+      <c r="U13" s="6">
         <f>VLOOKUP(A13,[1]Sheet!$A:$T,20,0)</f>
         <v>650</v>
       </c>
-      <c r="V13" s="24"/>
+      <c r="V13" s="6"/>
       <c r="W13" s="6">
         <f t="shared" si="6"/>
         <v>19.308905701429065</v>
@@ -6850,7 +6864,10 @@
         <f t="shared" si="7"/>
         <v>600</v>
       </c>
-      <c r="AK13" s="6"/>
+      <c r="AK13" s="6">
+        <f t="shared" si="8"/>
+        <v>60.669000000000004</v>
+      </c>
       <c r="AL13" s="6"/>
       <c r="AM13" s="6"/>
       <c r="AN13" s="6"/>
@@ -6917,11 +6934,11 @@
       <c r="T14" s="4">
         <v>200</v>
       </c>
-      <c r="U14" s="24">
+      <c r="U14" s="6">
         <f>VLOOKUP(A14,[1]Sheet!$A:$T,20,0)</f>
         <v>500</v>
       </c>
-      <c r="V14" s="24"/>
+      <c r="V14" s="6"/>
       <c r="W14" s="6">
         <f t="shared" si="6"/>
         <v>52.027027027027025</v>
@@ -6967,7 +6984,10 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="AK14" s="6"/>
+      <c r="AK14" s="6">
+        <f t="shared" si="8"/>
+        <v>1.85</v>
+      </c>
       <c r="AL14" s="6"/>
       <c r="AM14" s="6"/>
       <c r="AN14" s="6"/>
@@ -7031,17 +7051,17 @@
         <v>16.9358</v>
       </c>
       <c r="S15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>39.093000000000004</v>
       </c>
       <c r="T15" s="4">
         <v>100</v>
       </c>
-      <c r="U15" s="24">
+      <c r="U15" s="6">
         <f>VLOOKUP(A15,[1]Sheet!$A:$T,20,0)</f>
         <v>150</v>
       </c>
-      <c r="V15" s="24"/>
+      <c r="V15" s="6"/>
       <c r="W15" s="6">
         <f t="shared" si="6"/>
         <v>18.596346201537571</v>
@@ -7085,7 +7105,10 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AK15" s="6"/>
+      <c r="AK15" s="6">
+        <f t="shared" si="8"/>
+        <v>16.9358</v>
+      </c>
       <c r="AL15" s="6"/>
       <c r="AM15" s="6"/>
       <c r="AN15" s="6"/>
@@ -7155,11 +7178,11 @@
       <c r="T16" s="4">
         <v>650</v>
       </c>
-      <c r="U16" s="24">
+      <c r="U16" s="6">
         <f>VLOOKUP(A16,[1]Sheet!$A:$T,20,0)</f>
         <v>700</v>
       </c>
-      <c r="V16" s="24"/>
+      <c r="V16" s="6"/>
       <c r="W16" s="6">
         <f t="shared" si="6"/>
         <v>18.804780876494021</v>
@@ -7205,7 +7228,10 @@
         <f t="shared" si="7"/>
         <v>162.5</v>
       </c>
-      <c r="AK16" s="6"/>
+      <c r="AK16" s="6">
+        <f t="shared" si="8"/>
+        <v>12.55</v>
+      </c>
       <c r="AL16" s="6"/>
       <c r="AM16" s="6"/>
       <c r="AN16" s="6"/>
@@ -7276,8 +7302,8 @@
         <f t="shared" si="5"/>
         <v>163</v>
       </c>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
       <c r="W17" s="6">
         <f t="shared" si="6"/>
         <v>13.009259259259258</v>
@@ -7321,7 +7347,10 @@
         <f t="shared" si="7"/>
         <v>65.2</v>
       </c>
-      <c r="AK17" s="6"/>
+      <c r="AK17" s="6">
+        <f t="shared" si="8"/>
+        <v>8.64</v>
+      </c>
       <c r="AL17" s="6"/>
       <c r="AM17" s="6"/>
       <c r="AN17" s="6"/>
@@ -7385,17 +7414,17 @@
         <v>70.5762</v>
       </c>
       <c r="S18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>461.96200000000005</v>
       </c>
       <c r="T18" s="4">
         <v>750</v>
       </c>
-      <c r="U18" s="24">
+      <c r="U18" s="6">
         <f>VLOOKUP(A18,[1]Sheet!$A:$T,20,0)</f>
         <v>900</v>
       </c>
-      <c r="V18" s="24"/>
+      <c r="V18" s="6"/>
       <c r="W18" s="6">
         <f t="shared" si="6"/>
         <v>19.081234183761666</v>
@@ -7439,7 +7468,10 @@
         <f t="shared" si="7"/>
         <v>750</v>
       </c>
-      <c r="AK18" s="6"/>
+      <c r="AK18" s="6">
+        <f t="shared" si="8"/>
+        <v>70.5762</v>
+      </c>
       <c r="AL18" s="6"/>
       <c r="AM18" s="6"/>
       <c r="AN18" s="6"/>
@@ -7503,17 +7535,17 @@
         <v>8.5001999999999995</v>
       </c>
       <c r="S19" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6.7099999999999866</v>
       </c>
       <c r="T19" s="4">
         <v>40</v>
       </c>
-      <c r="U19" s="24">
+      <c r="U19" s="6">
         <f>VLOOKUP(A19,[1]Sheet!$A:$T,20,0)</f>
         <v>80</v>
       </c>
-      <c r="V19" s="24"/>
+      <c r="V19" s="6"/>
       <c r="W19" s="6">
         <f t="shared" si="6"/>
         <v>18.9163784381544</v>
@@ -7559,7 +7591,10 @@
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="AK19" s="6"/>
+      <c r="AK19" s="6">
+        <f t="shared" si="8"/>
+        <v>8.5001999999999995</v>
+      </c>
       <c r="AL19" s="6"/>
       <c r="AM19" s="6"/>
       <c r="AN19" s="6"/>
@@ -7627,11 +7662,11 @@
       <c r="T20" s="4">
         <v>90</v>
       </c>
-      <c r="U20" s="24">
+      <c r="U20" s="6">
         <f>VLOOKUP(A20,[1]Sheet!$A:$T,20,0)</f>
         <v>170</v>
       </c>
-      <c r="V20" s="24"/>
+      <c r="V20" s="6"/>
       <c r="W20" s="6">
         <f t="shared" si="6"/>
         <v>18.488372093023255</v>
@@ -7675,7 +7710,10 @@
         <f t="shared" si="7"/>
         <v>36</v>
       </c>
-      <c r="AK20" s="6"/>
+      <c r="AK20" s="6">
+        <f t="shared" si="8"/>
+        <v>3.44</v>
+      </c>
       <c r="AL20" s="6"/>
       <c r="AM20" s="6"/>
       <c r="AN20" s="6"/>
@@ -7739,17 +7777,17 @@
         <v>58.996200000000002</v>
       </c>
       <c r="S21" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>398.15600000000001</v>
       </c>
       <c r="T21" s="4">
         <v>650</v>
       </c>
-      <c r="U21" s="24">
+      <c r="U21" s="6">
         <f>VLOOKUP(A21,[1]Sheet!$A:$T,20,0)</f>
         <v>760</v>
       </c>
-      <c r="V21" s="24"/>
+      <c r="V21" s="6"/>
       <c r="W21" s="6">
         <f t="shared" si="6"/>
         <v>19.26881731365749</v>
@@ -7793,7 +7831,10 @@
         <f t="shared" si="7"/>
         <v>650</v>
       </c>
-      <c r="AK21" s="6"/>
+      <c r="AK21" s="6">
+        <f t="shared" si="8"/>
+        <v>58.996200000000002</v>
+      </c>
       <c r="AL21" s="6"/>
       <c r="AM21" s="6"/>
       <c r="AN21" s="6"/>
@@ -7857,18 +7898,18 @@
         <v>96.8</v>
       </c>
       <c r="S22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>516</v>
       </c>
       <c r="T22" s="4">
-        <f t="shared" ref="T22:T39" si="9">U22</f>
+        <f t="shared" ref="T22:T39" si="10">U22</f>
         <v>700</v>
       </c>
-      <c r="U22" s="24">
+      <c r="U22" s="6">
         <f>VLOOKUP(A22,[1]Sheet!$A:$T,20,0)</f>
         <v>700</v>
       </c>
-      <c r="V22" s="24"/>
+      <c r="V22" s="6"/>
       <c r="W22" s="6">
         <f t="shared" si="6"/>
         <v>16.900826446280991</v>
@@ -7914,7 +7955,10 @@
         <f t="shared" si="7"/>
         <v>154</v>
       </c>
-      <c r="AK22" s="6"/>
+      <c r="AK22" s="6">
+        <f t="shared" si="8"/>
+        <v>21.295999999999999</v>
+      </c>
       <c r="AL22" s="6"/>
       <c r="AM22" s="6"/>
       <c r="AN22" s="6"/>
@@ -7982,14 +8026,14 @@
         <v>65.498800000000003</v>
       </c>
       <c r="T23" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
-      <c r="U23" s="24">
+      <c r="U23" s="6">
         <f>VLOOKUP(A23,[1]Sheet!$A:$T,20,0)</f>
         <v>80</v>
       </c>
-      <c r="V23" s="24"/>
+      <c r="V23" s="6"/>
       <c r="W23" s="6">
         <f t="shared" si="6"/>
         <v>15.700581668073928</v>
@@ -8035,7 +8079,10 @@
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="AK23" s="6"/>
+      <c r="AK23" s="6">
+        <f t="shared" si="8"/>
+        <v>8.5272000000000006</v>
+      </c>
       <c r="AL23" s="6"/>
       <c r="AM23" s="6"/>
       <c r="AN23" s="6"/>
@@ -8099,17 +8146,17 @@
         <v>20.069200000000002</v>
       </c>
       <c r="S24" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>105.875</v>
       </c>
       <c r="T24" s="4">
         <v>180</v>
       </c>
-      <c r="U24" s="24">
+      <c r="U24" s="6">
         <f>VLOOKUP(A24,[1]Sheet!$A:$T,20,0)</f>
         <v>200</v>
       </c>
-      <c r="V24" s="24"/>
+      <c r="V24" s="6"/>
       <c r="W24" s="6">
         <f t="shared" si="6"/>
         <v>18.693470591752536</v>
@@ -8153,7 +8200,10 @@
         <f t="shared" si="7"/>
         <v>180</v>
       </c>
-      <c r="AK24" s="6"/>
+      <c r="AK24" s="6">
+        <f t="shared" si="8"/>
+        <v>20.069200000000002</v>
+      </c>
       <c r="AL24" s="6"/>
       <c r="AM24" s="6"/>
       <c r="AN24" s="6"/>
@@ -8217,18 +8267,18 @@
         <v>58.2</v>
       </c>
       <c r="S25" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>364</v>
       </c>
       <c r="T25" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>600</v>
       </c>
-      <c r="U25" s="24">
+      <c r="U25" s="6">
         <f>VLOOKUP(A25,[1]Sheet!$A:$T,20,0)</f>
         <v>600</v>
       </c>
-      <c r="V25" s="24"/>
+      <c r="V25" s="6"/>
       <c r="W25" s="6">
         <f t="shared" si="6"/>
         <v>19.054982817869416</v>
@@ -8272,7 +8322,10 @@
         <f t="shared" si="7"/>
         <v>54</v>
       </c>
-      <c r="AK25" s="6"/>
+      <c r="AK25" s="6">
+        <f t="shared" si="8"/>
+        <v>5.2380000000000004</v>
+      </c>
       <c r="AL25" s="6"/>
       <c r="AM25" s="6"/>
       <c r="AN25" s="6"/>
@@ -8340,14 +8393,14 @@
         <v>355.40000000000009</v>
       </c>
       <c r="T26" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>500</v>
       </c>
-      <c r="U26" s="24">
+      <c r="U26" s="6">
         <f>VLOOKUP(A26,[1]Sheet!$A:$T,20,0)</f>
         <v>500</v>
       </c>
-      <c r="V26" s="24"/>
+      <c r="V26" s="6"/>
       <c r="W26" s="6">
         <f t="shared" si="6"/>
         <v>14.880478087649401</v>
@@ -8393,7 +8446,10 @@
         <f t="shared" si="7"/>
         <v>45</v>
       </c>
-      <c r="AK26" s="6"/>
+      <c r="AK26" s="6">
+        <f t="shared" si="8"/>
+        <v>4.5179999999999998</v>
+      </c>
       <c r="AL26" s="6"/>
       <c r="AM26" s="6"/>
       <c r="AN26" s="6"/>
@@ -8461,14 +8517,14 @@
         <v>321</v>
       </c>
       <c r="T27" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>400</v>
       </c>
-      <c r="U27" s="24">
+      <c r="U27" s="6">
         <f>VLOOKUP(A27,[1]Sheet!$A:$T,20,0)</f>
         <v>400</v>
       </c>
-      <c r="V27" s="24"/>
+      <c r="V27" s="6"/>
       <c r="W27" s="6">
         <f t="shared" si="6"/>
         <v>13.926829268292684</v>
@@ -8512,7 +8568,10 @@
         <f t="shared" si="7"/>
         <v>60</v>
       </c>
-      <c r="AK27" s="6"/>
+      <c r="AK27" s="6">
+        <f t="shared" si="8"/>
+        <v>6.1499999999999995</v>
+      </c>
       <c r="AL27" s="6"/>
       <c r="AM27" s="6"/>
       <c r="AN27" s="6"/>
@@ -8576,18 +8635,18 @@
         <v>72.474000000000004</v>
       </c>
       <c r="S28" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>347.00900000000013</v>
       </c>
       <c r="T28" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>347</v>
       </c>
-      <c r="U28" s="24">
+      <c r="U28" s="6">
         <f>VLOOKUP(A28,[1]Sheet!$A:$T,20,0)</f>
         <v>347</v>
       </c>
-      <c r="V28" s="24"/>
+      <c r="V28" s="6"/>
       <c r="W28" s="6">
         <f t="shared" si="6"/>
         <v>14.999875817534566</v>
@@ -8631,7 +8690,10 @@
         <f t="shared" si="7"/>
         <v>347</v>
       </c>
-      <c r="AK28" s="6"/>
+      <c r="AK28" s="6">
+        <f t="shared" si="8"/>
+        <v>72.474000000000004</v>
+      </c>
       <c r="AL28" s="6"/>
       <c r="AM28" s="6"/>
       <c r="AN28" s="6"/>
@@ -8699,14 +8761,14 @@
         <v>377.6</v>
       </c>
       <c r="T29" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>600</v>
       </c>
-      <c r="U29" s="24">
+      <c r="U29" s="6">
         <f>VLOOKUP(A29,[1]Sheet!$A:$T,20,0)</f>
         <v>600</v>
       </c>
-      <c r="V29" s="24"/>
+      <c r="V29" s="6"/>
       <c r="W29" s="6">
         <f t="shared" si="6"/>
         <v>18.793103448275861</v>
@@ -8752,7 +8814,10 @@
         <f t="shared" si="7"/>
         <v>240</v>
       </c>
-      <c r="AK29" s="6"/>
+      <c r="AK29" s="6">
+        <f t="shared" si="8"/>
+        <v>18.559999999999999</v>
+      </c>
       <c r="AL29" s="6"/>
       <c r="AM29" s="6"/>
       <c r="AN29" s="6"/>
@@ -8822,11 +8887,11 @@
       <c r="T30" s="4">
         <v>900</v>
       </c>
-      <c r="U30" s="24">
+      <c r="U30" s="6">
         <f>VLOOKUP(A30,[1]Sheet!$A:$T,20,0)</f>
         <v>1000</v>
       </c>
-      <c r="V30" s="24"/>
+      <c r="V30" s="6"/>
       <c r="W30" s="6">
         <f t="shared" si="6"/>
         <v>19.088397790055247</v>
@@ -8872,7 +8937,10 @@
         <f t="shared" si="7"/>
         <v>360</v>
       </c>
-      <c r="AK30" s="6"/>
+      <c r="AK30" s="6">
+        <f t="shared" si="8"/>
+        <v>28.960000000000004</v>
+      </c>
       <c r="AL30" s="6"/>
       <c r="AM30" s="6"/>
       <c r="AN30" s="6"/>
@@ -8940,14 +9008,14 @@
         <v>451.6</v>
       </c>
       <c r="T31" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>800</v>
       </c>
-      <c r="U31" s="24">
+      <c r="U31" s="6">
         <f>VLOOKUP(A31,[1]Sheet!$A:$T,20,0)</f>
         <v>800</v>
       </c>
-      <c r="V31" s="24"/>
+      <c r="V31" s="6"/>
       <c r="W31" s="6">
         <f t="shared" si="6"/>
         <v>16.56549520766773</v>
@@ -8993,7 +9061,10 @@
         <f t="shared" si="7"/>
         <v>320</v>
       </c>
-      <c r="AK31" s="6"/>
+      <c r="AK31" s="6">
+        <f t="shared" si="8"/>
+        <v>25.040000000000003</v>
+      </c>
       <c r="AL31" s="6"/>
       <c r="AM31" s="6"/>
       <c r="AN31" s="6"/>
@@ -9057,18 +9128,18 @@
         <v>34.4</v>
       </c>
       <c r="S32" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>119</v>
       </c>
       <c r="T32" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>250</v>
       </c>
-      <c r="U32" s="24">
+      <c r="U32" s="6">
         <f>VLOOKUP(A32,[1]Sheet!$A:$T,20,0)</f>
         <v>250</v>
       </c>
-      <c r="V32" s="24"/>
+      <c r="V32" s="6"/>
       <c r="W32" s="6">
         <f t="shared" si="6"/>
         <v>18.808139534883722</v>
@@ -9112,7 +9183,10 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="AK32" s="6"/>
+      <c r="AK32" s="6">
+        <f t="shared" si="8"/>
+        <v>10.319999999999999</v>
+      </c>
       <c r="AL32" s="6"/>
       <c r="AM32" s="6"/>
       <c r="AN32" s="6"/>
@@ -9182,11 +9256,11 @@
       <c r="T33" s="4">
         <v>250</v>
       </c>
-      <c r="U33" s="24">
+      <c r="U33" s="6">
         <f>VLOOKUP(A33,[1]Sheet!$A:$T,20,0)</f>
         <v>270</v>
       </c>
-      <c r="V33" s="24"/>
+      <c r="V33" s="6"/>
       <c r="W33" s="6">
         <f t="shared" si="6"/>
         <v>18.987305373916378</v>
@@ -9230,7 +9304,10 @@
         <f t="shared" si="7"/>
         <v>250</v>
       </c>
-      <c r="AK33" s="6"/>
+      <c r="AK33" s="6">
+        <f t="shared" si="8"/>
+        <v>18.779599999999999</v>
+      </c>
       <c r="AL33" s="6"/>
       <c r="AM33" s="6"/>
       <c r="AN33" s="6"/>
@@ -9297,11 +9374,11 @@
       <c r="T34" s="4">
         <v>40</v>
       </c>
-      <c r="U34" s="24">
+      <c r="U34" s="6">
         <f>VLOOKUP(A34,[1]Sheet!$A:$T,20,0)</f>
         <v>160</v>
       </c>
-      <c r="V34" s="24"/>
+      <c r="V34" s="6"/>
       <c r="W34" s="6">
         <f t="shared" si="6"/>
         <v>20.411206507004067</v>
@@ -9345,7 +9422,10 @@
         <f t="shared" si="7"/>
         <v>40</v>
       </c>
-      <c r="AK34" s="6"/>
+      <c r="AK34" s="6">
+        <f t="shared" si="8"/>
+        <v>18.589199999999998</v>
+      </c>
       <c r="AL34" s="6"/>
       <c r="AM34" s="6"/>
       <c r="AN34" s="6"/>
@@ -9411,18 +9491,18 @@
         <v>31.792000000000002</v>
       </c>
       <c r="S35" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>157.13200000000001</v>
       </c>
       <c r="T35" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>200</v>
       </c>
-      <c r="U35" s="24">
+      <c r="U35" s="6">
         <f>VLOOKUP(A35,[1]Sheet!$A:$T,20,0)</f>
         <v>200</v>
       </c>
-      <c r="V35" s="24"/>
+      <c r="V35" s="6"/>
       <c r="W35" s="6">
         <f t="shared" si="6"/>
         <v>16.348389531957725</v>
@@ -9466,7 +9546,10 @@
         <f t="shared" si="7"/>
         <v>200</v>
       </c>
-      <c r="AK35" s="6"/>
+      <c r="AK35" s="6">
+        <f t="shared" si="8"/>
+        <v>31.792000000000002</v>
+      </c>
       <c r="AL35" s="6"/>
       <c r="AM35" s="6"/>
       <c r="AN35" s="6"/>
@@ -9483,104 +9566,107 @@
       <c r="AY35" s="6"/>
     </row>
     <row r="36" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="16">
         <v>239</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17">
+      <c r="D36" s="16"/>
+      <c r="E36" s="16">
         <v>106</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="16">
         <v>133</v>
       </c>
-      <c r="G36" s="18">
+      <c r="G36" s="17">
         <v>0.35</v>
       </c>
-      <c r="H36" s="17"/>
-      <c r="I36" s="20" t="s">
+      <c r="H36" s="16"/>
+      <c r="I36" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="J36" s="17"/>
-      <c r="K36" s="17">
+      <c r="J36" s="16"/>
+      <c r="K36" s="16">
         <v>106</v>
       </c>
-      <c r="L36" s="17">
+      <c r="L36" s="16">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17"/>
-      <c r="O36" s="17">
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16">
         <v>0</v>
       </c>
-      <c r="P36" s="17"/>
-      <c r="Q36" s="17"/>
-      <c r="R36" s="17">
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16">
         <f t="shared" si="3"/>
         <v>21.2</v>
       </c>
-      <c r="S36" s="19"/>
+      <c r="S36" s="18"/>
       <c r="T36" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>700</v>
       </c>
-      <c r="U36" s="24">
+      <c r="U36" s="6">
         <f>VLOOKUP(A36,[1]Sheet!$A:$T,20,0)</f>
         <v>700</v>
       </c>
-      <c r="V36" s="24"/>
+      <c r="V36" s="6"/>
       <c r="W36" s="6">
         <f t="shared" si="6"/>
         <v>39.29245283018868</v>
       </c>
-      <c r="X36" s="17">
+      <c r="X36" s="16">
         <f t="shared" si="4"/>
         <v>6.2735849056603774</v>
       </c>
-      <c r="Y36" s="17">
+      <c r="Y36" s="16">
         <v>11.4</v>
       </c>
-      <c r="Z36" s="17">
+      <c r="Z36" s="16">
         <v>0</v>
       </c>
-      <c r="AA36" s="17">
+      <c r="AA36" s="16">
         <v>0</v>
       </c>
-      <c r="AB36" s="17">
+      <c r="AB36" s="16">
         <v>0</v>
       </c>
-      <c r="AC36" s="17">
+      <c r="AC36" s="16">
         <v>0</v>
       </c>
-      <c r="AD36" s="17">
+      <c r="AD36" s="16">
         <v>0</v>
       </c>
-      <c r="AE36" s="17">
+      <c r="AE36" s="16">
         <v>0</v>
       </c>
-      <c r="AF36" s="17">
+      <c r="AF36" s="16">
         <v>0</v>
       </c>
-      <c r="AG36" s="17">
+      <c r="AG36" s="16">
         <v>0</v>
       </c>
-      <c r="AH36" s="17">
+      <c r="AH36" s="16">
         <v>0</v>
       </c>
-      <c r="AI36" s="17" t="s">
+      <c r="AI36" s="16" t="s">
         <v>159</v>
       </c>
       <c r="AJ36" s="6">
         <f t="shared" si="7"/>
         <v>244.99999999999997</v>
       </c>
-      <c r="AK36" s="6"/>
+      <c r="AK36" s="6">
+        <f t="shared" si="8"/>
+        <v>7.419999999999999</v>
+      </c>
       <c r="AL36" s="6"/>
       <c r="AM36" s="6"/>
       <c r="AN36" s="6"/>
@@ -9646,18 +9732,18 @@
         <v>42.488399999999999</v>
       </c>
       <c r="S37" s="4">
-        <f t="shared" ref="S37:S57" si="10">15*R37-Q37-P37-O37-F37</f>
+        <f t="shared" ref="S37:S57" si="11">15*R37-Q37-P37-O37-F37</f>
         <v>284.00200000000001</v>
       </c>
       <c r="T37" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>250</v>
       </c>
-      <c r="U37" s="24">
+      <c r="U37" s="6">
         <f>VLOOKUP(A37,[1]Sheet!$A:$T,20,0)</f>
         <v>250</v>
       </c>
-      <c r="V37" s="24"/>
+      <c r="V37" s="6"/>
       <c r="W37" s="6">
         <f t="shared" si="6"/>
         <v>14.19973451577372</v>
@@ -9701,7 +9787,10 @@
         <f t="shared" si="7"/>
         <v>250</v>
       </c>
-      <c r="AK37" s="6"/>
+      <c r="AK37" s="6">
+        <f t="shared" si="8"/>
+        <v>42.488399999999999</v>
+      </c>
       <c r="AL37" s="6"/>
       <c r="AM37" s="6"/>
       <c r="AN37" s="6"/>
@@ -9748,7 +9837,7 @@
         <v>335</v>
       </c>
       <c r="L38" s="6">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
         <v>-24</v>
       </c>
       <c r="M38" s="6"/>
@@ -9759,28 +9848,28 @@
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
       <c r="R38" s="6">
-        <f t="shared" ref="R38:R69" si="12">E38/5</f>
+        <f t="shared" ref="R38:R69" si="13">E38/5</f>
         <v>62.2</v>
       </c>
       <c r="S38" s="4">
+        <f t="shared" si="11"/>
+        <v>503</v>
+      </c>
+      <c r="T38" s="4">
         <f t="shared" si="10"/>
-        <v>503</v>
-      </c>
-      <c r="T38" s="4">
-        <f t="shared" si="9"/>
         <v>650</v>
       </c>
-      <c r="U38" s="24">
+      <c r="U38" s="6">
         <f>VLOOKUP(A38,[1]Sheet!$A:$T,20,0)</f>
         <v>650</v>
       </c>
-      <c r="V38" s="24"/>
+      <c r="V38" s="6"/>
       <c r="W38" s="6">
         <f t="shared" si="6"/>
         <v>17.363344051446944</v>
       </c>
       <c r="X38" s="6">
-        <f t="shared" ref="X38:X69" si="13">(F38+O38+P38+Q38)/R38</f>
+        <f t="shared" ref="X38:X69" si="14">(F38+O38+P38+Q38)/R38</f>
         <v>6.913183279742765</v>
       </c>
       <c r="Y38" s="6">
@@ -9818,7 +9907,10 @@
         <f t="shared" si="7"/>
         <v>195</v>
       </c>
-      <c r="AK38" s="6"/>
+      <c r="AK38" s="6">
+        <f t="shared" si="8"/>
+        <v>18.66</v>
+      </c>
       <c r="AL38" s="6"/>
       <c r="AM38" s="6"/>
       <c r="AN38" s="6"/>
@@ -9867,7 +9959,7 @@
         <v>129.9</v>
       </c>
       <c r="L39" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>5.157999999999987</v>
       </c>
       <c r="M39" s="6"/>
@@ -9878,28 +9970,28 @@
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>27.011599999999998</v>
       </c>
       <c r="S39" s="4">
+        <f t="shared" si="11"/>
+        <v>211.53899999999999</v>
+      </c>
+      <c r="T39" s="4">
         <f t="shared" si="10"/>
-        <v>211.53899999999999</v>
-      </c>
-      <c r="T39" s="4">
-        <f t="shared" si="9"/>
         <v>280</v>
       </c>
-      <c r="U39" s="24">
+      <c r="U39" s="6">
         <f>VLOOKUP(A39,[1]Sheet!$A:$T,20,0)</f>
         <v>280</v>
       </c>
-      <c r="V39" s="24"/>
+      <c r="V39" s="6"/>
       <c r="W39" s="6">
         <f t="shared" si="6"/>
         <v>17.534503694708942</v>
       </c>
       <c r="X39" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.1685868293622006</v>
       </c>
       <c r="Y39" s="6">
@@ -9937,7 +10029,10 @@
         <f t="shared" si="7"/>
         <v>280</v>
       </c>
-      <c r="AK39" s="6"/>
+      <c r="AK39" s="6">
+        <f t="shared" si="8"/>
+        <v>27.011599999999998</v>
+      </c>
       <c r="AL39" s="6"/>
       <c r="AM39" s="6"/>
       <c r="AN39" s="6"/>
@@ -9986,7 +10081,7 @@
         <v>338.5</v>
       </c>
       <c r="L40" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>10.552000000000021</v>
       </c>
       <c r="M40" s="6"/>
@@ -9997,27 +10092,27 @@
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>69.810400000000001</v>
       </c>
       <c r="S40" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>376.59099999999995</v>
       </c>
       <c r="T40" s="4">
         <v>650</v>
       </c>
-      <c r="U40" s="24">
+      <c r="U40" s="6">
         <f>VLOOKUP(A40,[1]Sheet!$A:$T,20,0)</f>
         <v>700</v>
       </c>
-      <c r="V40" s="24"/>
+      <c r="V40" s="6"/>
       <c r="W40" s="6">
         <f t="shared" si="6"/>
         <v>18.91645084400032</v>
       </c>
       <c r="X40" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.6055172295245406</v>
       </c>
       <c r="Y40" s="6">
@@ -10055,7 +10150,10 @@
         <f t="shared" si="7"/>
         <v>650</v>
       </c>
-      <c r="AK40" s="6"/>
+      <c r="AK40" s="6">
+        <f t="shared" si="8"/>
+        <v>69.810400000000001</v>
+      </c>
       <c r="AL40" s="6"/>
       <c r="AM40" s="6"/>
       <c r="AN40" s="6"/>
@@ -10104,7 +10202,7 @@
         <v>386</v>
       </c>
       <c r="L41" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-115</v>
       </c>
       <c r="M41" s="6"/>
@@ -10117,24 +10215,24 @@
         <v>500</v>
       </c>
       <c r="R41" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>54.2</v>
       </c>
       <c r="S41" s="4"/>
       <c r="T41" s="4">
         <v>200</v>
       </c>
-      <c r="U41" s="24">
+      <c r="U41" s="6">
         <f>VLOOKUP(A41,[1]Sheet!$A:$T,20,0)</f>
         <v>900</v>
       </c>
-      <c r="V41" s="24"/>
+      <c r="V41" s="6"/>
       <c r="W41" s="6">
         <f t="shared" si="6"/>
         <v>25.461254612546124</v>
       </c>
       <c r="X41" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>21.771217712177119</v>
       </c>
       <c r="Y41" s="6">
@@ -10172,7 +10270,10 @@
         <f t="shared" si="7"/>
         <v>70</v>
       </c>
-      <c r="AK41" s="6"/>
+      <c r="AK41" s="6">
+        <f t="shared" si="8"/>
+        <v>18.97</v>
+      </c>
       <c r="AL41" s="6"/>
       <c r="AM41" s="6"/>
       <c r="AN41" s="6"/>
@@ -10221,7 +10322,7 @@
         <v>317</v>
       </c>
       <c r="L42" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-15</v>
       </c>
       <c r="M42" s="6"/>
@@ -10232,25 +10333,25 @@
       <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
       <c r="R42" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>60.4</v>
       </c>
       <c r="S42" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>383</v>
       </c>
       <c r="T42" s="4">
         <f t="shared" si="5"/>
         <v>383</v>
       </c>
-      <c r="U42" s="24"/>
-      <c r="V42" s="24"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
       <c r="W42" s="6">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="X42" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.6589403973509942</v>
       </c>
       <c r="Y42" s="6">
@@ -10288,7 +10389,10 @@
         <f t="shared" si="7"/>
         <v>157.03</v>
       </c>
-      <c r="AK42" s="6"/>
+      <c r="AK42" s="6">
+        <f t="shared" si="8"/>
+        <v>24.763999999999999</v>
+      </c>
       <c r="AL42" s="6"/>
       <c r="AM42" s="6"/>
       <c r="AN42" s="6"/>
@@ -10337,7 +10441,7 @@
         <v>178</v>
       </c>
       <c r="L43" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-7</v>
       </c>
       <c r="M43" s="6"/>
@@ -10348,28 +10452,28 @@
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
       <c r="R43" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>34.200000000000003</v>
       </c>
       <c r="S43" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>282</v>
       </c>
       <c r="T43" s="4">
         <f>U43</f>
         <v>340</v>
       </c>
-      <c r="U43" s="24">
+      <c r="U43" s="6">
         <f>VLOOKUP(A43,[1]Sheet!$A:$T,20,0)</f>
         <v>340</v>
       </c>
-      <c r="V43" s="24"/>
+      <c r="V43" s="6"/>
       <c r="W43" s="6">
         <f t="shared" si="6"/>
         <v>16.695906432748536</v>
       </c>
       <c r="X43" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.7543859649122799</v>
       </c>
       <c r="Y43" s="6">
@@ -10407,7 +10511,10 @@
         <f t="shared" si="7"/>
         <v>139.4</v>
       </c>
-      <c r="AK43" s="6"/>
+      <c r="AK43" s="6">
+        <f t="shared" si="8"/>
+        <v>14.022</v>
+      </c>
       <c r="AL43" s="6"/>
       <c r="AM43" s="6"/>
       <c r="AN43" s="6"/>
@@ -10454,7 +10561,7 @@
         <v>173</v>
       </c>
       <c r="L44" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2</v>
       </c>
       <c r="M44" s="6"/>
@@ -10465,7 +10572,7 @@
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
       <c r="R44" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>34.200000000000003</v>
       </c>
       <c r="S44" s="4">
@@ -10476,14 +10583,14 @@
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
-      <c r="U44" s="24"/>
-      <c r="V44" s="24"/>
+      <c r="U44" s="6"/>
+      <c r="V44" s="6"/>
       <c r="W44" s="6">
         <f t="shared" si="6"/>
         <v>14.005847953216373</v>
       </c>
       <c r="X44" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.654970760233917</v>
       </c>
       <c r="Y44" s="6">
@@ -10516,14 +10623,17 @@
       <c r="AH44" s="6">
         <v>43.8</v>
       </c>
-      <c r="AI44" s="23" t="s">
+      <c r="AI44" s="22" t="s">
         <v>50</v>
       </c>
       <c r="AJ44" s="6">
         <f t="shared" si="7"/>
         <v>4.32</v>
       </c>
-      <c r="AK44" s="6"/>
+      <c r="AK44" s="6">
+        <f t="shared" si="8"/>
+        <v>12.312000000000001</v>
+      </c>
       <c r="AL44" s="6"/>
       <c r="AM44" s="6"/>
       <c r="AN44" s="6"/>
@@ -10570,7 +10680,7 @@
         <v>65</v>
       </c>
       <c r="L45" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2</v>
       </c>
       <c r="M45" s="6"/>
@@ -10581,7 +10691,7 @@
       <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
       <c r="R45" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>12.6</v>
       </c>
       <c r="S45" s="4">
@@ -10592,14 +10702,14 @@
         <f t="shared" si="5"/>
         <v>106</v>
       </c>
-      <c r="U45" s="24"/>
-      <c r="V45" s="24"/>
+      <c r="U45" s="6"/>
+      <c r="V45" s="6"/>
       <c r="W45" s="6">
         <f t="shared" si="6"/>
         <v>11.984126984126984</v>
       </c>
       <c r="X45" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.5714285714285716</v>
       </c>
       <c r="Y45" s="6">
@@ -10637,7 +10747,10 @@
         <f t="shared" si="7"/>
         <v>34.980000000000004</v>
       </c>
-      <c r="AK45" s="6"/>
+      <c r="AK45" s="6">
+        <f t="shared" si="8"/>
+        <v>4.1580000000000004</v>
+      </c>
       <c r="AL45" s="6"/>
       <c r="AM45" s="6"/>
       <c r="AN45" s="6"/>
@@ -10684,7 +10797,7 @@
         <v>67</v>
       </c>
       <c r="L46" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2</v>
       </c>
       <c r="M46" s="6"/>
@@ -10695,28 +10808,28 @@
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
       <c r="R46" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
       <c r="S46" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23</v>
       </c>
       <c r="T46" s="4">
-        <f t="shared" ref="T46:T49" si="14">U46</f>
+        <f t="shared" ref="T46:T49" si="15">U46</f>
         <v>50</v>
       </c>
-      <c r="U46" s="24">
+      <c r="U46" s="6">
         <f>VLOOKUP(A46,[1]Sheet!$A:$T,20,0)</f>
         <v>50</v>
       </c>
-      <c r="V46" s="24"/>
+      <c r="V46" s="6"/>
       <c r="W46" s="6">
         <f t="shared" si="6"/>
         <v>17.076923076923077</v>
       </c>
       <c r="X46" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>13.23076923076923</v>
       </c>
       <c r="Y46" s="6">
@@ -10754,7 +10867,10 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="AK46" s="6"/>
+      <c r="AK46" s="6">
+        <f t="shared" si="8"/>
+        <v>5.2</v>
+      </c>
       <c r="AL46" s="6"/>
       <c r="AM46" s="6"/>
       <c r="AN46" s="6"/>
@@ -10801,7 +10917,7 @@
         <v>38</v>
       </c>
       <c r="L47" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-6</v>
       </c>
       <c r="M47" s="6"/>
@@ -10812,7 +10928,7 @@
       <c r="P47" s="6"/>
       <c r="Q47" s="6"/>
       <c r="R47" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.4</v>
       </c>
       <c r="S47" s="4">
@@ -10820,20 +10936,20 @@
         <v>49.600000000000009</v>
       </c>
       <c r="T47" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>80</v>
       </c>
-      <c r="U47" s="24">
+      <c r="U47" s="6">
         <f>VLOOKUP(A47,[1]Sheet!$A:$T,20,0)</f>
         <v>80</v>
       </c>
-      <c r="V47" s="24"/>
+      <c r="V47" s="6"/>
       <c r="W47" s="6">
         <f t="shared" si="6"/>
         <v>18.75</v>
       </c>
       <c r="X47" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.25</v>
       </c>
       <c r="Y47" s="6">
@@ -10871,7 +10987,10 @@
         <f t="shared" si="7"/>
         <v>26.400000000000002</v>
       </c>
-      <c r="AK47" s="6"/>
+      <c r="AK47" s="6">
+        <f t="shared" si="8"/>
+        <v>2.1120000000000001</v>
+      </c>
       <c r="AL47" s="6"/>
       <c r="AM47" s="6"/>
       <c r="AN47" s="6"/>
@@ -10920,7 +11039,7 @@
         <v>286.8</v>
       </c>
       <c r="L48" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.2319999999999709</v>
       </c>
       <c r="M48" s="6"/>
@@ -10931,27 +11050,27 @@
       <c r="P48" s="6"/>
       <c r="Q48" s="6"/>
       <c r="R48" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>59.006399999999999</v>
       </c>
       <c r="S48" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>135.49700000000001</v>
       </c>
       <c r="T48" s="4">
         <v>400</v>
       </c>
-      <c r="U48" s="24">
+      <c r="U48" s="6">
         <f>VLOOKUP(A48,[1]Sheet!$A:$T,20,0)</f>
         <v>600</v>
       </c>
-      <c r="V48" s="24"/>
+      <c r="V48" s="6"/>
       <c r="W48" s="6">
         <f t="shared" si="6"/>
         <v>19.482615445104258</v>
       </c>
       <c r="X48" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.703689769245369</v>
       </c>
       <c r="Y48" s="6">
@@ -10989,7 +11108,10 @@
         <f t="shared" si="7"/>
         <v>400</v>
       </c>
-      <c r="AK48" s="6"/>
+      <c r="AK48" s="6">
+        <f t="shared" si="8"/>
+        <v>59.006399999999999</v>
+      </c>
       <c r="AL48" s="6"/>
       <c r="AM48" s="6"/>
       <c r="AN48" s="6"/>
@@ -11036,7 +11158,7 @@
         <v>88</v>
       </c>
       <c r="L49" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-33</v>
       </c>
       <c r="M49" s="6"/>
@@ -11047,7 +11169,7 @@
       <c r="P49" s="6"/>
       <c r="Q49" s="6"/>
       <c r="R49" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
       <c r="S49" s="4">
@@ -11055,20 +11177,20 @@
         <v>33</v>
       </c>
       <c r="T49" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>70</v>
       </c>
-      <c r="U49" s="24">
+      <c r="U49" s="6">
         <f>VLOOKUP(A49,[1]Sheet!$A:$T,20,0)</f>
         <v>70</v>
       </c>
-      <c r="V49" s="24"/>
+      <c r="V49" s="6"/>
       <c r="W49" s="6">
         <f t="shared" si="6"/>
         <v>17.363636363636363</v>
       </c>
       <c r="X49" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>11</v>
       </c>
       <c r="Y49" s="6">
@@ -11106,7 +11228,10 @@
         <f t="shared" si="7"/>
         <v>28</v>
       </c>
-      <c r="AK49" s="6"/>
+      <c r="AK49" s="6">
+        <f t="shared" si="8"/>
+        <v>4.4000000000000004</v>
+      </c>
       <c r="AL49" s="6"/>
       <c r="AM49" s="6"/>
       <c r="AN49" s="6"/>
@@ -11153,7 +11278,7 @@
         <v>19.8</v>
       </c>
       <c r="L50" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.11100000000000065</v>
       </c>
       <c r="M50" s="6"/>
@@ -11164,25 +11289,25 @@
       <c r="P50" s="6"/>
       <c r="Q50" s="6"/>
       <c r="R50" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.9378000000000002</v>
       </c>
       <c r="S50" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>31.580000000000002</v>
       </c>
       <c r="T50" s="4">
         <f t="shared" si="5"/>
         <v>32</v>
       </c>
-      <c r="U50" s="24"/>
-      <c r="V50" s="24"/>
+      <c r="U50" s="6"/>
+      <c r="V50" s="6"/>
       <c r="W50" s="6">
         <f t="shared" si="6"/>
         <v>15.106658540301689</v>
       </c>
       <c r="X50" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.9802935649347342</v>
       </c>
       <c r="Y50" s="6">
@@ -11215,14 +11340,17 @@
       <c r="AH50" s="6">
         <v>4.3317999999999994</v>
       </c>
-      <c r="AI50" s="23" t="s">
+      <c r="AI50" s="22" t="s">
         <v>156</v>
       </c>
       <c r="AJ50" s="6">
         <f t="shared" si="7"/>
         <v>32</v>
       </c>
-      <c r="AK50" s="6"/>
+      <c r="AK50" s="6">
+        <f t="shared" si="8"/>
+        <v>3.9378000000000002</v>
+      </c>
       <c r="AL50" s="6"/>
       <c r="AM50" s="6"/>
       <c r="AN50" s="6"/>
@@ -11269,7 +11397,7 @@
         <v>25.2</v>
       </c>
       <c r="L51" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.46499999999999986</v>
       </c>
       <c r="M51" s="6"/>
@@ -11280,7 +11408,7 @@
       <c r="P51" s="6"/>
       <c r="Q51" s="6"/>
       <c r="R51" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.133</v>
       </c>
       <c r="S51" s="4">
@@ -11291,14 +11419,14 @@
         <f t="shared" si="5"/>
         <v>33</v>
       </c>
-      <c r="U51" s="24"/>
-      <c r="V51" s="24"/>
+      <c r="U51" s="6"/>
+      <c r="V51" s="6"/>
       <c r="W51" s="6">
         <f t="shared" si="6"/>
         <v>13.947983635300993</v>
       </c>
       <c r="X51" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.5189947399181767</v>
       </c>
       <c r="Y51" s="6">
@@ -11336,7 +11464,10 @@
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="AK51" s="6"/>
+      <c r="AK51" s="6">
+        <f t="shared" si="8"/>
+        <v>5.133</v>
+      </c>
       <c r="AL51" s="6"/>
       <c r="AM51" s="6"/>
       <c r="AN51" s="6"/>
@@ -11383,7 +11514,7 @@
         <v>9.1</v>
       </c>
       <c r="L52" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3.6619999999999999</v>
       </c>
       <c r="M52" s="6"/>
@@ -11396,7 +11527,7 @@
         <v>150</v>
       </c>
       <c r="R52" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0875999999999999</v>
       </c>
       <c r="S52" s="4"/>
@@ -11404,17 +11535,17 @@
         <f>U52</f>
         <v>30</v>
       </c>
-      <c r="U52" s="24">
+      <c r="U52" s="6">
         <f>VLOOKUP(A52,[1]Sheet!$A:$T,20,0)</f>
         <v>30</v>
       </c>
-      <c r="V52" s="24"/>
+      <c r="V52" s="6"/>
       <c r="W52" s="6">
         <f t="shared" si="6"/>
         <v>165.23538065465246</v>
       </c>
       <c r="X52" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>137.65171018756897</v>
       </c>
       <c r="Y52" s="6">
@@ -11454,7 +11585,10 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="AK52" s="6"/>
+      <c r="AK52" s="6">
+        <f t="shared" si="8"/>
+        <v>1.0875999999999999</v>
+      </c>
       <c r="AL52" s="6"/>
       <c r="AM52" s="6"/>
       <c r="AN52" s="6"/>
@@ -11503,7 +11637,7 @@
         <v>32</v>
       </c>
       <c r="L53" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M53" s="6"/>
@@ -11514,7 +11648,7 @@
       <c r="P53" s="6"/>
       <c r="Q53" s="6"/>
       <c r="R53" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6.4</v>
       </c>
       <c r="S53" s="4">
@@ -11525,14 +11659,14 @@
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="U53" s="24"/>
-      <c r="V53" s="24"/>
+      <c r="U53" s="6"/>
+      <c r="V53" s="6"/>
       <c r="W53" s="6">
         <f t="shared" si="6"/>
         <v>14.0625</v>
       </c>
       <c r="X53" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.78125</v>
       </c>
       <c r="Y53" s="6">
@@ -11565,14 +11699,17 @@
       <c r="AH53" s="6">
         <v>5.6</v>
       </c>
-      <c r="AI53" s="23" t="s">
+      <c r="AI53" s="22" t="s">
         <v>43</v>
       </c>
       <c r="AJ53" s="6">
         <f t="shared" si="7"/>
         <v>5.25</v>
       </c>
-      <c r="AK53" s="6"/>
+      <c r="AK53" s="6">
+        <f t="shared" si="8"/>
+        <v>1.6</v>
+      </c>
       <c r="AL53" s="6"/>
       <c r="AM53" s="6"/>
       <c r="AN53" s="6"/>
@@ -11621,7 +11758,7 @@
         <v>52</v>
       </c>
       <c r="L54" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-6.6890000000000001</v>
       </c>
       <c r="M54" s="6"/>
@@ -11634,22 +11771,22 @@
         <v>200</v>
       </c>
       <c r="R54" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9.0622000000000007</v>
       </c>
       <c r="S54" s="4"/>
       <c r="T54" s="4"/>
-      <c r="U54" s="24">
+      <c r="U54" s="6">
         <f>VLOOKUP(A54,[1]Sheet!$A:$T,20,0)</f>
         <v>200</v>
       </c>
-      <c r="V54" s="24"/>
+      <c r="V54" s="6"/>
       <c r="W54" s="6">
         <f t="shared" si="6"/>
         <v>27.094855553839022</v>
       </c>
       <c r="X54" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>27.094855553839022</v>
       </c>
       <c r="Y54" s="6">
@@ -11687,7 +11824,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK54" s="6"/>
+      <c r="AK54" s="6">
+        <f t="shared" si="8"/>
+        <v>9.0622000000000007</v>
+      </c>
       <c r="AL54" s="6"/>
       <c r="AM54" s="6"/>
       <c r="AN54" s="6"/>
@@ -11734,7 +11874,7 @@
         <v>74</v>
       </c>
       <c r="L55" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-9</v>
       </c>
       <c r="M55" s="6"/>
@@ -11745,25 +11885,25 @@
       <c r="P55" s="6"/>
       <c r="Q55" s="6"/>
       <c r="R55" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
       <c r="S55" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>92</v>
       </c>
       <c r="T55" s="4">
         <f t="shared" si="5"/>
         <v>92</v>
       </c>
-      <c r="U55" s="24"/>
-      <c r="V55" s="24"/>
+      <c r="U55" s="6"/>
+      <c r="V55" s="6"/>
       <c r="W55" s="6">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="X55" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.9230769230769234</v>
       </c>
       <c r="Y55" s="6">
@@ -11801,7 +11941,10 @@
         <f t="shared" si="7"/>
         <v>24.840000000000003</v>
       </c>
-      <c r="AK55" s="6"/>
+      <c r="AK55" s="6">
+        <f t="shared" si="8"/>
+        <v>3.5100000000000002</v>
+      </c>
       <c r="AL55" s="6"/>
       <c r="AM55" s="6"/>
       <c r="AN55" s="6"/>
@@ -11848,7 +11991,7 @@
         <v>150</v>
       </c>
       <c r="L56" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4</v>
       </c>
       <c r="M56" s="6"/>
@@ -11859,7 +12002,7 @@
       <c r="P56" s="6"/>
       <c r="Q56" s="6"/>
       <c r="R56" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>29.2</v>
       </c>
       <c r="S56" s="4">
@@ -11867,20 +12010,20 @@
         <v>232</v>
       </c>
       <c r="T56" s="4">
-        <f t="shared" ref="T56:T57" si="15">U56</f>
+        <f t="shared" ref="T56:T57" si="16">U56</f>
         <v>450</v>
       </c>
-      <c r="U56" s="24">
+      <c r="U56" s="6">
         <f>VLOOKUP(A56,[1]Sheet!$A:$T,20,0)</f>
         <v>450</v>
       </c>
-      <c r="V56" s="24"/>
+      <c r="V56" s="6"/>
       <c r="W56" s="6">
         <f t="shared" si="6"/>
         <v>17.465753424657535</v>
       </c>
       <c r="X56" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.0547945205479454</v>
       </c>
       <c r="Y56" s="6">
@@ -11920,7 +12063,10 @@
         <f t="shared" si="7"/>
         <v>135</v>
       </c>
-      <c r="AK56" s="6"/>
+      <c r="AK56" s="6">
+        <f t="shared" si="8"/>
+        <v>8.76</v>
+      </c>
       <c r="AL56" s="6"/>
       <c r="AM56" s="6"/>
       <c r="AN56" s="6"/>
@@ -11952,7 +12098,7 @@
       <c r="E57" s="6">
         <v>614</v>
       </c>
-      <c r="F57" s="21">
+      <c r="F57" s="20">
         <f>254+F58</f>
         <v>238</v>
       </c>
@@ -11970,7 +12116,7 @@
         <v>626</v>
       </c>
       <c r="L57" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-12</v>
       </c>
       <c r="M57" s="6"/>
@@ -11981,28 +12127,28 @@
       <c r="P57" s="6"/>
       <c r="Q57" s="6"/>
       <c r="R57" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>122.8</v>
       </c>
       <c r="S57" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>710</v>
       </c>
       <c r="T57" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>850</v>
       </c>
-      <c r="U57" s="24">
+      <c r="U57" s="6">
         <f>VLOOKUP(A57,[1]Sheet!$A:$T,20,0)</f>
         <v>850</v>
       </c>
-      <c r="V57" s="24"/>
+      <c r="V57" s="6"/>
       <c r="W57" s="6">
         <f t="shared" si="6"/>
         <v>16.140065146579804</v>
       </c>
       <c r="X57" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.2182410423452765</v>
       </c>
       <c r="Y57" s="6">
@@ -12042,7 +12188,10 @@
         <f t="shared" si="7"/>
         <v>348.5</v>
       </c>
-      <c r="AK57" s="6"/>
+      <c r="AK57" s="6">
+        <f t="shared" si="8"/>
+        <v>50.347999999999999</v>
+      </c>
       <c r="AL57" s="6"/>
       <c r="AM57" s="6"/>
       <c r="AN57" s="6"/>
@@ -12059,99 +12208,102 @@
       <c r="AY57" s="6"/>
     </row>
     <row r="58" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="10">
         <v>-16</v>
       </c>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="21">
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="20">
         <v>-16</v>
       </c>
-      <c r="G58" s="12">
+      <c r="G58" s="11">
         <v>0</v>
       </c>
-      <c r="H58" s="11"/>
-      <c r="I58" s="11" t="s">
+      <c r="H58" s="10"/>
+      <c r="I58" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="J58" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K58" s="11">
+      <c r="K58" s="10">
         <v>3</v>
       </c>
-      <c r="L58" s="11">
-        <f t="shared" si="11"/>
+      <c r="L58" s="10">
+        <f t="shared" si="12"/>
         <v>-3</v>
       </c>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="11">
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10">
         <v>0</v>
       </c>
-      <c r="P58" s="11"/>
-      <c r="Q58" s="11"/>
-      <c r="R58" s="11">
-        <f t="shared" si="12"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="S58" s="13"/>
+      <c r="S58" s="12"/>
       <c r="T58" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U58" s="24"/>
-      <c r="V58" s="24"/>
+      <c r="U58" s="6"/>
+      <c r="V58" s="6"/>
       <c r="W58" s="6" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X58" s="11" t="e">
-        <f t="shared" si="13"/>
+      <c r="X58" s="10" t="e">
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y58" s="11">
+      <c r="Y58" s="10">
         <v>0</v>
       </c>
-      <c r="Z58" s="11">
+      <c r="Z58" s="10">
         <v>0</v>
       </c>
-      <c r="AA58" s="11">
+      <c r="AA58" s="10">
         <v>0</v>
       </c>
-      <c r="AB58" s="11">
+      <c r="AB58" s="10">
         <v>0</v>
       </c>
-      <c r="AC58" s="11">
+      <c r="AC58" s="10">
         <v>0</v>
       </c>
-      <c r="AD58" s="11">
+      <c r="AD58" s="10">
         <v>0</v>
       </c>
-      <c r="AE58" s="11">
+      <c r="AE58" s="10">
         <v>0</v>
       </c>
-      <c r="AF58" s="11">
+      <c r="AF58" s="10">
         <v>0</v>
       </c>
-      <c r="AG58" s="11">
+      <c r="AG58" s="10">
         <v>0</v>
       </c>
-      <c r="AH58" s="11">
+      <c r="AH58" s="10">
         <v>0</v>
       </c>
-      <c r="AI58" s="11"/>
+      <c r="AI58" s="10"/>
       <c r="AJ58" s="6">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK58" s="6"/>
+      <c r="AK58" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="AL58" s="6"/>
       <c r="AM58" s="6"/>
       <c r="AN58" s="6"/>
@@ -12200,7 +12352,7 @@
         <v>608.6</v>
       </c>
       <c r="L59" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>29.062999999999988</v>
       </c>
       <c r="M59" s="6"/>
@@ -12211,7 +12363,7 @@
       <c r="P59" s="6"/>
       <c r="Q59" s="6"/>
       <c r="R59" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>127.5326</v>
       </c>
       <c r="S59" s="4">
@@ -12219,20 +12371,20 @@
         <v>979.13679999999999</v>
       </c>
       <c r="T59" s="4">
-        <f t="shared" ref="T59:T62" si="16">U59</f>
+        <f t="shared" ref="T59:T62" si="17">U59</f>
         <v>979</v>
       </c>
-      <c r="U59" s="24">
+      <c r="U59" s="6">
         <f>VLOOKUP(A59,[1]Sheet!$A:$T,20,0)</f>
         <v>979</v>
       </c>
-      <c r="V59" s="24"/>
+      <c r="V59" s="6"/>
       <c r="W59" s="6">
         <f t="shared" si="6"/>
         <v>12.998927333089735</v>
       </c>
       <c r="X59" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.3224587281996918</v>
       </c>
       <c r="Y59" s="6">
@@ -12270,7 +12422,10 @@
         <f t="shared" si="7"/>
         <v>979</v>
       </c>
-      <c r="AK59" s="6"/>
+      <c r="AK59" s="6">
+        <f t="shared" si="8"/>
+        <v>127.5326</v>
+      </c>
       <c r="AL59" s="6"/>
       <c r="AM59" s="6"/>
       <c r="AN59" s="6"/>
@@ -12317,7 +12472,7 @@
         <v>61</v>
       </c>
       <c r="L60" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-26</v>
       </c>
       <c r="M60" s="6"/>
@@ -12330,22 +12485,22 @@
         <v>200</v>
       </c>
       <c r="R60" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7</v>
       </c>
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
-      <c r="U60" s="24">
+      <c r="U60" s="6">
         <f>VLOOKUP(A60,[1]Sheet!$A:$T,20,0)</f>
         <v>150</v>
       </c>
-      <c r="V60" s="24"/>
+      <c r="V60" s="6"/>
       <c r="W60" s="6">
         <f t="shared" si="6"/>
         <v>44.142857142857146</v>
       </c>
       <c r="X60" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>44.142857142857146</v>
       </c>
       <c r="Y60" s="6">
@@ -12383,7 +12538,10 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK60" s="6"/>
+      <c r="AK60" s="6">
+        <f t="shared" si="8"/>
+        <v>2.4499999999999997</v>
+      </c>
       <c r="AL60" s="6"/>
       <c r="AM60" s="6"/>
       <c r="AN60" s="6"/>
@@ -12432,7 +12590,7 @@
         <v>78</v>
       </c>
       <c r="L61" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.179000000000002</v>
       </c>
       <c r="M61" s="6"/>
@@ -12443,27 +12601,27 @@
       <c r="P61" s="6"/>
       <c r="Q61" s="6"/>
       <c r="R61" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.835800000000001</v>
       </c>
       <c r="S61" s="4">
-        <f t="shared" ref="S61" si="17">12*R61-Q61-P61-O61-F61</f>
+        <f t="shared" ref="S61" si="18">12*R61-Q61-P61-O61-F61</f>
         <v>120.84760000000001</v>
       </c>
       <c r="T61" s="4">
         <v>230</v>
       </c>
-      <c r="U61" s="24">
+      <c r="U61" s="6">
         <f>VLOOKUP(A61,[1]Sheet!$A:$T,20,0)</f>
         <v>300</v>
       </c>
-      <c r="V61" s="24"/>
+      <c r="V61" s="6"/>
       <c r="W61" s="6">
         <f t="shared" si="6"/>
         <v>18.892761969714194</v>
       </c>
       <c r="X61" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.368708874827921</v>
       </c>
       <c r="Y61" s="6">
@@ -12501,7 +12659,10 @@
         <f t="shared" si="7"/>
         <v>230</v>
       </c>
-      <c r="AK61" s="6"/>
+      <c r="AK61" s="6">
+        <f t="shared" si="8"/>
+        <v>15.835800000000001</v>
+      </c>
       <c r="AL61" s="6"/>
       <c r="AM61" s="6"/>
       <c r="AN61" s="6"/>
@@ -12550,7 +12711,7 @@
         <v>536</v>
       </c>
       <c r="L62" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="M62" s="6"/>
@@ -12561,7 +12722,7 @@
       <c r="P62" s="6"/>
       <c r="Q62" s="6"/>
       <c r="R62" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>107.6</v>
       </c>
       <c r="S62" s="4">
@@ -12569,20 +12730,20 @@
         <v>742.59999999999991</v>
       </c>
       <c r="T62" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>900</v>
       </c>
-      <c r="U62" s="24">
+      <c r="U62" s="6">
         <f>VLOOKUP(A62,[1]Sheet!$A:$T,20,0)</f>
         <v>900</v>
       </c>
-      <c r="V62" s="24"/>
+      <c r="V62" s="6"/>
       <c r="W62" s="6">
         <f t="shared" si="6"/>
         <v>12.46282527881041</v>
       </c>
       <c r="X62" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0985130111524164</v>
       </c>
       <c r="Y62" s="6">
@@ -12622,7 +12783,10 @@
         <f t="shared" si="7"/>
         <v>369</v>
       </c>
-      <c r="AK62" s="6"/>
+      <c r="AK62" s="6">
+        <f t="shared" si="8"/>
+        <v>44.115999999999993</v>
+      </c>
       <c r="AL62" s="6"/>
       <c r="AM62" s="6"/>
       <c r="AN62" s="6"/>
@@ -12671,7 +12835,7 @@
         <v>109.5</v>
       </c>
       <c r="L63" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.8670000000000044</v>
       </c>
       <c r="M63" s="6"/>
@@ -12682,7 +12846,7 @@
       <c r="P63" s="6"/>
       <c r="Q63" s="6"/>
       <c r="R63" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>22.273400000000002</v>
       </c>
       <c r="S63" s="4"/>
@@ -12690,17 +12854,17 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U63" s="24">
+      <c r="U63" s="6">
         <f>VLOOKUP(A63,[1]Sheet!$A:$T,20,0)</f>
         <v>300</v>
       </c>
-      <c r="V63" s="24"/>
+      <c r="V63" s="6"/>
       <c r="W63" s="6">
         <f t="shared" si="6"/>
         <v>20.653245575439762</v>
       </c>
       <c r="X63" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20.653245575439762</v>
       </c>
       <c r="Y63" s="6">
@@ -12733,14 +12897,17 @@
       <c r="AH63" s="6">
         <v>37.538600000000002</v>
       </c>
-      <c r="AI63" s="22" t="s">
+      <c r="AI63" s="21" t="s">
         <v>45</v>
       </c>
       <c r="AJ63" s="6">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AK63" s="6"/>
+      <c r="AK63" s="6">
+        <f t="shared" si="8"/>
+        <v>22.273400000000002</v>
+      </c>
       <c r="AL63" s="6"/>
       <c r="AM63" s="6"/>
       <c r="AN63" s="6"/>
@@ -12789,7 +12956,7 @@
         <v>145</v>
       </c>
       <c r="L64" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-61</v>
       </c>
       <c r="M64" s="6"/>
@@ -12800,25 +12967,25 @@
       <c r="P64" s="6"/>
       <c r="Q64" s="6"/>
       <c r="R64" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.8</v>
       </c>
       <c r="S64" s="4">
-        <f t="shared" ref="S64:S86" si="18">15*R64-Q64-P64-O64-F64</f>
+        <f t="shared" ref="S64:S86" si="19">15*R64-Q64-P64-O64-F64</f>
         <v>116</v>
       </c>
       <c r="T64" s="4">
         <f t="shared" si="5"/>
         <v>116</v>
       </c>
-      <c r="U64" s="24"/>
-      <c r="V64" s="24"/>
+      <c r="U64" s="6"/>
+      <c r="V64" s="6"/>
       <c r="W64" s="6">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="X64" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.0952380952380949</v>
       </c>
       <c r="Y64" s="6">
@@ -12856,7 +13023,10 @@
         <f t="shared" si="7"/>
         <v>34.799999999999997</v>
       </c>
-      <c r="AK64" s="6"/>
+      <c r="AK64" s="6">
+        <f t="shared" si="8"/>
+        <v>5.04</v>
+      </c>
       <c r="AL64" s="6"/>
       <c r="AM64" s="6"/>
       <c r="AN64" s="6"/>
@@ -12905,7 +13075,7 @@
         <v>330</v>
       </c>
       <c r="L65" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-11</v>
       </c>
       <c r="M65" s="6"/>
@@ -12916,28 +13086,28 @@
       <c r="P65" s="6"/>
       <c r="Q65" s="6"/>
       <c r="R65" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>63.8</v>
       </c>
       <c r="S65" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>431</v>
       </c>
       <c r="T65" s="4">
         <f>U65</f>
         <v>700</v>
       </c>
-      <c r="U65" s="24">
+      <c r="U65" s="6">
         <f>VLOOKUP(A65,[1]Sheet!$A:$T,20,0)</f>
         <v>700</v>
       </c>
-      <c r="V65" s="24"/>
+      <c r="V65" s="6"/>
       <c r="W65" s="6">
         <f t="shared" si="6"/>
         <v>19.216300940438874</v>
       </c>
       <c r="X65" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.2445141065830718</v>
       </c>
       <c r="Y65" s="6">
@@ -12975,7 +13145,10 @@
         <f t="shared" si="7"/>
         <v>126</v>
       </c>
-      <c r="AK65" s="6"/>
+      <c r="AK65" s="6">
+        <f t="shared" si="8"/>
+        <v>11.483999999999998</v>
+      </c>
       <c r="AL65" s="6"/>
       <c r="AM65" s="6"/>
       <c r="AN65" s="6"/>
@@ -13022,7 +13195,7 @@
         <v>12</v>
       </c>
       <c r="L66" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M66" s="6"/>
@@ -13033,25 +13206,25 @@
       <c r="P66" s="6"/>
       <c r="Q66" s="6"/>
       <c r="R66" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.4</v>
       </c>
       <c r="S66" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>11</v>
       </c>
       <c r="T66" s="4">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="U66" s="24"/>
-      <c r="V66" s="24"/>
+      <c r="U66" s="6"/>
+      <c r="V66" s="6"/>
       <c r="W66" s="6">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="X66" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.416666666666668</v>
       </c>
       <c r="Y66" s="6">
@@ -13091,7 +13264,10 @@
         <f t="shared" si="7"/>
         <v>2.42</v>
       </c>
-      <c r="AK66" s="6"/>
+      <c r="AK66" s="6">
+        <f t="shared" si="8"/>
+        <v>0.52800000000000002</v>
+      </c>
       <c r="AL66" s="6"/>
       <c r="AM66" s="6"/>
       <c r="AN66" s="6"/>
@@ -13138,7 +13314,7 @@
         <v>105</v>
       </c>
       <c r="L67" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-59</v>
       </c>
       <c r="M67" s="6"/>
@@ -13149,28 +13325,28 @@
       <c r="P67" s="6"/>
       <c r="Q67" s="6"/>
       <c r="R67" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>9.1999999999999993</v>
       </c>
       <c r="S67" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>53</v>
       </c>
       <c r="T67" s="4">
-        <f t="shared" ref="T67:T71" si="19">U67</f>
+        <f t="shared" ref="T67:T71" si="20">U67</f>
         <v>70</v>
       </c>
-      <c r="U67" s="24">
+      <c r="U67" s="6">
         <f>VLOOKUP(A67,[1]Sheet!$A:$T,20,0)</f>
         <v>70</v>
       </c>
-      <c r="V67" s="24"/>
+      <c r="V67" s="6"/>
       <c r="W67" s="6">
         <f t="shared" si="6"/>
         <v>16.847826086956523</v>
       </c>
       <c r="X67" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.2391304347826093</v>
       </c>
       <c r="Y67" s="6">
@@ -13208,7 +13384,10 @@
         <f t="shared" si="7"/>
         <v>58.8</v>
       </c>
-      <c r="AK67" s="6"/>
+      <c r="AK67" s="6">
+        <f t="shared" si="8"/>
+        <v>7.7279999999999989</v>
+      </c>
       <c r="AL67" s="6"/>
       <c r="AM67" s="6"/>
       <c r="AN67" s="6"/>
@@ -13257,7 +13436,7 @@
         <v>600</v>
       </c>
       <c r="L68" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-19</v>
       </c>
       <c r="M68" s="6"/>
@@ -13268,28 +13447,28 @@
       <c r="P68" s="6"/>
       <c r="Q68" s="6"/>
       <c r="R68" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>116.2</v>
       </c>
       <c r="S68" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>723</v>
       </c>
       <c r="T68" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1000</v>
       </c>
-      <c r="U68" s="24">
+      <c r="U68" s="6">
         <f>VLOOKUP(A68,[1]Sheet!$A:$T,20,0)</f>
         <v>1000</v>
       </c>
-      <c r="V68" s="24"/>
+      <c r="V68" s="6"/>
       <c r="W68" s="6">
         <f t="shared" si="6"/>
         <v>17.383820998278829</v>
       </c>
       <c r="X68" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.7779690189328736</v>
       </c>
       <c r="Y68" s="6">
@@ -13327,7 +13506,10 @@
         <f t="shared" si="7"/>
         <v>350</v>
       </c>
-      <c r="AK68" s="6"/>
+      <c r="AK68" s="6">
+        <f t="shared" si="8"/>
+        <v>40.67</v>
+      </c>
       <c r="AL68" s="6"/>
       <c r="AM68" s="6"/>
       <c r="AN68" s="6"/>
@@ -13374,7 +13556,7 @@
         <v>286</v>
       </c>
       <c r="L69" s="6">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-90</v>
       </c>
       <c r="M69" s="6"/>
@@ -13385,27 +13567,27 @@
       <c r="P69" s="6"/>
       <c r="Q69" s="6"/>
       <c r="R69" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>39.200000000000003</v>
       </c>
       <c r="S69" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>195</v>
       </c>
       <c r="T69" s="4">
         <v>350</v>
       </c>
-      <c r="U69" s="24">
+      <c r="U69" s="6">
         <f>VLOOKUP(A69,[1]Sheet!$A:$T,20,0)</f>
         <v>700</v>
       </c>
-      <c r="V69" s="24"/>
+      <c r="V69" s="6"/>
       <c r="W69" s="6">
         <f t="shared" si="6"/>
         <v>18.954081632653061</v>
       </c>
       <c r="X69" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.025510204081632</v>
       </c>
       <c r="Y69" s="6">
@@ -13445,7 +13627,10 @@
         <f t="shared" si="7"/>
         <v>122.49999999999999</v>
       </c>
-      <c r="AK69" s="6"/>
+      <c r="AK69" s="6">
+        <f t="shared" si="8"/>
+        <v>13.72</v>
+      </c>
       <c r="AL69" s="6"/>
       <c r="AM69" s="6"/>
       <c r="AN69" s="6"/>
@@ -13494,7 +13679,7 @@
         <v>305.60000000000002</v>
       </c>
       <c r="L70" s="6">
-        <f t="shared" ref="L70:L101" si="20">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="21">E70-K70</f>
         <v>-5.4159999999999968</v>
       </c>
       <c r="M70" s="6"/>
@@ -13507,27 +13692,27 @@
         <v>200</v>
       </c>
       <c r="R70" s="6">
-        <f t="shared" ref="R70:R104" si="21">E70/5</f>
+        <f t="shared" ref="R70:R104" si="22">E70/5</f>
         <v>60.036800000000007</v>
       </c>
       <c r="S70" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>222.08600000000013</v>
       </c>
       <c r="T70" s="4">
         <v>450</v>
       </c>
-      <c r="U70" s="24">
+      <c r="U70" s="6">
         <f>VLOOKUP(A70,[1]Sheet!$A:$T,20,0)</f>
         <v>500</v>
       </c>
-      <c r="V70" s="24"/>
+      <c r="V70" s="6"/>
       <c r="W70" s="6">
         <f t="shared" si="6"/>
         <v>18.796238307171599</v>
       </c>
       <c r="X70" s="6">
-        <f t="shared" ref="X70:X104" si="22">(F70+O70+P70+Q70)/R70</f>
+        <f t="shared" ref="X70:X104" si="23">(F70+O70+P70+Q70)/R70</f>
         <v>11.300835487567625</v>
       </c>
       <c r="Y70" s="6">
@@ -13565,7 +13750,10 @@
         <f t="shared" si="7"/>
         <v>450</v>
       </c>
-      <c r="AK70" s="6"/>
+      <c r="AK70" s="6">
+        <f t="shared" si="8"/>
+        <v>60.036800000000007</v>
+      </c>
       <c r="AL70" s="6"/>
       <c r="AM70" s="6"/>
       <c r="AN70" s="6"/>
@@ -13614,7 +13802,7 @@
         <v>325.3</v>
       </c>
       <c r="L71" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>17.334000000000003</v>
       </c>
       <c r="M71" s="6"/>
@@ -13627,28 +13815,28 @@
         <v>300</v>
       </c>
       <c r="R71" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>68.526800000000009</v>
       </c>
       <c r="S71" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>201.89100000000005</v>
       </c>
       <c r="T71" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>500</v>
       </c>
-      <c r="U71" s="24">
+      <c r="U71" s="6">
         <f>VLOOKUP(A71,[1]Sheet!$A:$T,20,0)</f>
         <v>500</v>
       </c>
-      <c r="V71" s="24"/>
+      <c r="V71" s="6"/>
       <c r="W71" s="6">
-        <f t="shared" ref="W71:W104" si="23">(F71+O71+P71+Q71+T71)/R71</f>
+        <f t="shared" ref="W71:W104" si="24">(F71+O71+P71+Q71+T71)/R71</f>
         <v>19.350254207113128</v>
       </c>
       <c r="X71" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.053838790079208</v>
       </c>
       <c r="Y71" s="6">
@@ -13683,10 +13871,13 @@
       </c>
       <c r="AI71" s="6"/>
       <c r="AJ71" s="6">
-        <f t="shared" ref="AJ71:AJ104" si="24">G71*T71</f>
+        <f t="shared" ref="AJ71:AJ104" si="25">G71*T71</f>
         <v>500</v>
       </c>
-      <c r="AK71" s="6"/>
+      <c r="AK71" s="6">
+        <f t="shared" ref="AK71:AK104" si="26">R71*G71</f>
+        <v>68.526800000000009</v>
+      </c>
       <c r="AL71" s="6"/>
       <c r="AM71" s="6"/>
       <c r="AN71" s="6"/>
@@ -13735,7 +13926,7 @@
         <v>316</v>
       </c>
       <c r="L72" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-49</v>
       </c>
       <c r="M72" s="6"/>
@@ -13748,24 +13939,24 @@
         <v>500</v>
       </c>
       <c r="R72" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>53.4</v>
       </c>
       <c r="S72" s="4"/>
       <c r="T72" s="4">
         <v>100</v>
       </c>
-      <c r="U72" s="24">
+      <c r="U72" s="6">
         <f>VLOOKUP(A72,[1]Sheet!$A:$T,20,0)</f>
         <v>800</v>
       </c>
-      <c r="V72" s="24"/>
+      <c r="V72" s="6"/>
       <c r="W72" s="6">
+        <f t="shared" si="24"/>
+        <v>20.430711610486892</v>
+      </c>
+      <c r="X72" s="6">
         <f t="shared" si="23"/>
-        <v>20.430711610486892</v>
-      </c>
-      <c r="X72" s="6">
-        <f t="shared" si="22"/>
         <v>18.558052434456929</v>
       </c>
       <c r="Y72" s="6">
@@ -13800,10 +13991,13 @@
       </c>
       <c r="AI72" s="6"/>
       <c r="AJ72" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>35</v>
       </c>
-      <c r="AK72" s="6"/>
+      <c r="AK72" s="6">
+        <f t="shared" si="26"/>
+        <v>18.689999999999998</v>
+      </c>
       <c r="AL72" s="6"/>
       <c r="AM72" s="6"/>
       <c r="AN72" s="6"/>
@@ -13852,7 +14046,7 @@
         <v>57</v>
       </c>
       <c r="L73" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-4</v>
       </c>
       <c r="M73" s="6"/>
@@ -13863,25 +14057,25 @@
       <c r="P73" s="6"/>
       <c r="Q73" s="6"/>
       <c r="R73" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>10.6</v>
       </c>
       <c r="S73" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>15</v>
       </c>
       <c r="T73" s="4">
-        <f t="shared" ref="T73:T103" si="25">ROUND(S73,0)</f>
+        <f t="shared" ref="T73:T103" si="27">ROUND(S73,0)</f>
         <v>15</v>
       </c>
-      <c r="U73" s="24"/>
-      <c r="V73" s="24"/>
+      <c r="U73" s="6"/>
+      <c r="V73" s="6"/>
       <c r="W73" s="6">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="X73" s="6">
         <f t="shared" si="23"/>
-        <v>15</v>
-      </c>
-      <c r="X73" s="6">
-        <f t="shared" si="22"/>
         <v>13.584905660377359</v>
       </c>
       <c r="Y73" s="6">
@@ -13916,10 +14110,13 @@
       </c>
       <c r="AI73" s="6"/>
       <c r="AJ73" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.5</v>
       </c>
-      <c r="AK73" s="6"/>
+      <c r="AK73" s="6">
+        <f t="shared" si="26"/>
+        <v>3.1799999999999997</v>
+      </c>
       <c r="AL73" s="6"/>
       <c r="AM73" s="6"/>
       <c r="AN73" s="6"/>
@@ -13968,7 +14165,7 @@
         <v>119</v>
       </c>
       <c r="L74" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-24</v>
       </c>
       <c r="M74" s="6"/>
@@ -13979,27 +14176,27 @@
       <c r="P74" s="6"/>
       <c r="Q74" s="6"/>
       <c r="R74" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>19</v>
       </c>
       <c r="S74" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>160</v>
       </c>
       <c r="T74" s="4">
         <v>230</v>
       </c>
-      <c r="U74" s="24">
+      <c r="U74" s="6">
         <f>VLOOKUP(A74,[1]Sheet!$A:$T,20,0)</f>
         <v>300</v>
       </c>
-      <c r="V74" s="24"/>
+      <c r="V74" s="6"/>
       <c r="W74" s="6">
+        <f t="shared" si="24"/>
+        <v>18.684210526315791</v>
+      </c>
+      <c r="X74" s="6">
         <f t="shared" si="23"/>
-        <v>18.684210526315791</v>
-      </c>
-      <c r="X74" s="6">
-        <f t="shared" si="22"/>
         <v>6.5789473684210522</v>
       </c>
       <c r="Y74" s="6">
@@ -14034,10 +14231,13 @@
       </c>
       <c r="AI74" s="6"/>
       <c r="AJ74" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>69</v>
       </c>
-      <c r="AK74" s="6"/>
+      <c r="AK74" s="6">
+        <f t="shared" si="26"/>
+        <v>5.7</v>
+      </c>
       <c r="AL74" s="6"/>
       <c r="AM74" s="6"/>
       <c r="AN74" s="6"/>
@@ -14086,7 +14286,7 @@
         <v>162</v>
       </c>
       <c r="L75" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-12</v>
       </c>
       <c r="M75" s="6"/>
@@ -14097,27 +14297,27 @@
       <c r="P75" s="6"/>
       <c r="Q75" s="6"/>
       <c r="R75" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>30</v>
       </c>
       <c r="S75" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>136</v>
       </c>
       <c r="T75" s="4">
         <v>250</v>
       </c>
-      <c r="U75" s="24">
+      <c r="U75" s="6">
         <f>VLOOKUP(A75,[1]Sheet!$A:$T,20,0)</f>
         <v>340</v>
       </c>
-      <c r="V75" s="24"/>
+      <c r="V75" s="6"/>
       <c r="W75" s="6">
+        <f t="shared" si="24"/>
+        <v>18.8</v>
+      </c>
+      <c r="X75" s="6">
         <f t="shared" si="23"/>
-        <v>18.8</v>
-      </c>
-      <c r="X75" s="6">
-        <f t="shared" si="22"/>
         <v>10.466666666666667</v>
       </c>
       <c r="Y75" s="6">
@@ -14152,10 +14352,13 @@
       </c>
       <c r="AI75" s="6"/>
       <c r="AJ75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>70</v>
       </c>
-      <c r="AK75" s="6"/>
+      <c r="AK75" s="6">
+        <f t="shared" si="26"/>
+        <v>8.4</v>
+      </c>
       <c r="AL75" s="6"/>
       <c r="AM75" s="6"/>
       <c r="AN75" s="6"/>
@@ -14204,7 +14407,7 @@
         <v>181</v>
       </c>
       <c r="L76" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-47</v>
       </c>
       <c r="M76" s="6"/>
@@ -14215,24 +14418,24 @@
       <c r="P76" s="6"/>
       <c r="Q76" s="6"/>
       <c r="R76" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>26.8</v>
       </c>
       <c r="S76" s="4"/>
       <c r="T76" s="4">
         <v>40</v>
       </c>
-      <c r="U76" s="24">
+      <c r="U76" s="6">
         <f>VLOOKUP(A76,[1]Sheet!$A:$T,20,0)</f>
         <v>100</v>
       </c>
-      <c r="V76" s="24"/>
+      <c r="V76" s="6"/>
       <c r="W76" s="6">
+        <f t="shared" si="24"/>
+        <v>22.46268656716418</v>
+      </c>
+      <c r="X76" s="6">
         <f t="shared" si="23"/>
-        <v>22.46268656716418</v>
-      </c>
-      <c r="X76" s="6">
-        <f t="shared" si="22"/>
         <v>20.970149253731343</v>
       </c>
       <c r="Y76" s="6">
@@ -14267,10 +14470,13 @@
       </c>
       <c r="AI76" s="6"/>
       <c r="AJ76" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>11.200000000000001</v>
       </c>
-      <c r="AK76" s="6"/>
+      <c r="AK76" s="6">
+        <f t="shared" si="26"/>
+        <v>7.5040000000000013</v>
+      </c>
       <c r="AL76" s="6"/>
       <c r="AM76" s="6"/>
       <c r="AN76" s="6"/>
@@ -14319,7 +14525,7 @@
         <v>683</v>
       </c>
       <c r="L77" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-29</v>
       </c>
       <c r="M77" s="6"/>
@@ -14330,7 +14536,7 @@
       <c r="P77" s="6"/>
       <c r="Q77" s="6"/>
       <c r="R77" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>130.80000000000001</v>
       </c>
       <c r="S77" s="4">
@@ -14338,17 +14544,17 @@
         <v>1060.2000000000003</v>
       </c>
       <c r="T77" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1060</v>
       </c>
-      <c r="U77" s="24"/>
-      <c r="V77" s="24"/>
+      <c r="U77" s="6"/>
+      <c r="V77" s="6"/>
       <c r="W77" s="6">
+        <f t="shared" si="24"/>
+        <v>13.998470948012232</v>
+      </c>
+      <c r="X77" s="6">
         <f t="shared" si="23"/>
-        <v>13.998470948012232</v>
-      </c>
-      <c r="X77" s="6">
-        <f t="shared" si="22"/>
         <v>5.8944954128440363</v>
       </c>
       <c r="Y77" s="6">
@@ -14383,10 +14589,13 @@
       </c>
       <c r="AI77" s="6"/>
       <c r="AJ77" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>296.8</v>
       </c>
-      <c r="AK77" s="6"/>
+      <c r="AK77" s="6">
+        <f t="shared" si="26"/>
+        <v>36.624000000000009</v>
+      </c>
       <c r="AL77" s="6"/>
       <c r="AM77" s="6"/>
       <c r="AN77" s="6"/>
@@ -14435,7 +14644,7 @@
         <v>217</v>
       </c>
       <c r="L78" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-6</v>
       </c>
       <c r="M78" s="6"/>
@@ -14446,28 +14655,28 @@
       <c r="P78" s="6"/>
       <c r="Q78" s="6"/>
       <c r="R78" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>42.2</v>
       </c>
       <c r="S78" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>278</v>
       </c>
       <c r="T78" s="4">
-        <f t="shared" ref="T78" si="26">U78</f>
+        <f t="shared" ref="T78" si="28">U78</f>
         <v>400</v>
       </c>
-      <c r="U78" s="24">
+      <c r="U78" s="6">
         <f>VLOOKUP(A78,[1]Sheet!$A:$T,20,0)</f>
         <v>400</v>
       </c>
-      <c r="V78" s="24"/>
+      <c r="V78" s="6"/>
       <c r="W78" s="6">
+        <f t="shared" si="24"/>
+        <v>17.890995260663505</v>
+      </c>
+      <c r="X78" s="6">
         <f t="shared" si="23"/>
-        <v>17.890995260663505</v>
-      </c>
-      <c r="X78" s="6">
-        <f t="shared" si="22"/>
         <v>8.4123222748815163</v>
       </c>
       <c r="Y78" s="6">
@@ -14502,10 +14711,13 @@
       </c>
       <c r="AI78" s="6"/>
       <c r="AJ78" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>160</v>
       </c>
-      <c r="AK78" s="6"/>
+      <c r="AK78" s="6">
+        <f t="shared" si="26"/>
+        <v>16.880000000000003</v>
+      </c>
       <c r="AL78" s="6"/>
       <c r="AM78" s="6"/>
       <c r="AN78" s="6"/>
@@ -14554,7 +14766,7 @@
         <v>159.1</v>
       </c>
       <c r="L79" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-128.57599999999999</v>
       </c>
       <c r="M79" s="6"/>
@@ -14569,26 +14781,26 @@
         <v>500</v>
       </c>
       <c r="R79" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.1048</v>
       </c>
       <c r="S79" s="4"/>
       <c r="T79" s="4">
         <v>1000</v>
       </c>
-      <c r="U79" s="24">
+      <c r="U79" s="6">
         <f>VLOOKUP(A79,[1]Sheet!$A:$T,20,0)</f>
         <v>1000</v>
       </c>
-      <c r="V79" s="26" t="s">
+      <c r="V79" s="7" t="s">
         <v>163</v>
       </c>
       <c r="W79" s="6">
+        <f t="shared" si="24"/>
+        <v>315.87242825317782</v>
+      </c>
+      <c r="X79" s="6">
         <f t="shared" si="23"/>
-        <v>315.87242825317782</v>
-      </c>
-      <c r="X79" s="6">
-        <f t="shared" si="22"/>
         <v>152.06689817848249</v>
       </c>
       <c r="Y79" s="6">
@@ -14625,10 +14837,13 @@
         <v>38</v>
       </c>
       <c r="AJ79" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1000</v>
       </c>
-      <c r="AK79" s="6"/>
+      <c r="AK79" s="6">
+        <f t="shared" si="26"/>
+        <v>6.1048</v>
+      </c>
       <c r="AL79" s="6"/>
       <c r="AM79" s="6"/>
       <c r="AN79" s="6"/>
@@ -14675,7 +14890,7 @@
         <v>2</v>
       </c>
       <c r="L80" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M80" s="6"/>
@@ -14686,62 +14901,65 @@
       <c r="P80" s="6"/>
       <c r="Q80" s="6"/>
       <c r="R80" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.4</v>
       </c>
       <c r="S80" s="4"/>
       <c r="T80" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U80" s="6"/>
+      <c r="V80" s="6"/>
+      <c r="W80" s="6">
+        <f t="shared" si="24"/>
+        <v>107.5</v>
+      </c>
+      <c r="X80" s="6">
+        <f t="shared" si="23"/>
+        <v>107.5</v>
+      </c>
+      <c r="Y80" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ80" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U80" s="24"/>
-      <c r="V80" s="24"/>
-      <c r="W80" s="6">
-        <f t="shared" si="23"/>
-        <v>107.5</v>
-      </c>
-      <c r="X80" s="6">
-        <f t="shared" si="22"/>
-        <v>107.5</v>
-      </c>
-      <c r="Y80" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH80" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI80" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ80" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK80" s="6"/>
+      <c r="AK80" s="6">
+        <f t="shared" si="26"/>
+        <v>0.13520000000000001</v>
+      </c>
       <c r="AL80" s="6"/>
       <c r="AM80" s="6"/>
       <c r="AN80" s="6"/>
@@ -14780,7 +14998,7 @@
       <c r="J81" s="6"/>
       <c r="K81" s="6"/>
       <c r="L81" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="M81" s="6"/>
@@ -14791,29 +15009,29 @@
       <c r="P81" s="6"/>
       <c r="Q81" s="6"/>
       <c r="R81" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="S81" s="4">
         <v>30</v>
       </c>
       <c r="T81" s="4">
-        <f t="shared" ref="T81:T86" si="27">U81</f>
+        <f t="shared" ref="T81:T86" si="29">U81</f>
         <v>60</v>
       </c>
-      <c r="U81" s="24">
+      <c r="U81" s="6">
         <f>VLOOKUP(A81,[1]Sheet!$A:$T,20,0)</f>
         <v>60</v>
       </c>
-      <c r="V81" s="24"/>
+      <c r="V81" s="6"/>
       <c r="W81" s="6" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X81" s="6" t="e">
         <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X81" s="6" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="Y81" s="6">
         <v>0</v>
       </c>
@@ -14848,10 +15066,13 @@
         <v>126</v>
       </c>
       <c r="AJ81" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>19.5</v>
       </c>
-      <c r="AK81" s="6"/>
+      <c r="AK81" s="6">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
       <c r="AL81" s="6"/>
       <c r="AM81" s="6"/>
       <c r="AN81" s="6"/>
@@ -14900,7 +15121,7 @@
         <v>211</v>
       </c>
       <c r="L82" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-25</v>
       </c>
       <c r="M82" s="6"/>
@@ -14913,24 +15134,24 @@
         <v>300</v>
       </c>
       <c r="R82" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>37.200000000000003</v>
       </c>
       <c r="S82" s="4"/>
       <c r="T82" s="4">
         <v>170</v>
       </c>
-      <c r="U82" s="24">
+      <c r="U82" s="6">
         <f>VLOOKUP(A82,[1]Sheet!$A:$T,20,0)</f>
         <v>600</v>
       </c>
-      <c r="V82" s="24"/>
+      <c r="V82" s="6"/>
       <c r="W82" s="6">
+        <f t="shared" si="24"/>
+        <v>22.231182795698924</v>
+      </c>
+      <c r="X82" s="6">
         <f t="shared" si="23"/>
-        <v>22.231182795698924</v>
-      </c>
-      <c r="X82" s="6">
-        <f t="shared" si="22"/>
         <v>17.661290322580644</v>
       </c>
       <c r="Y82" s="6">
@@ -14965,10 +15186,13 @@
       </c>
       <c r="AI82" s="6"/>
       <c r="AJ82" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>20.399999999999999</v>
       </c>
-      <c r="AK82" s="6"/>
+      <c r="AK82" s="6">
+        <f t="shared" si="26"/>
+        <v>4.4640000000000004</v>
+      </c>
       <c r="AL82" s="6"/>
       <c r="AM82" s="6"/>
       <c r="AN82" s="6"/>
@@ -15013,7 +15237,7 @@
         <v>32</v>
       </c>
       <c r="L83" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-5</v>
       </c>
       <c r="M83" s="6"/>
@@ -15026,25 +15250,25 @@
         <v>200</v>
       </c>
       <c r="R83" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5.4</v>
       </c>
       <c r="S83" s="4"/>
       <c r="T83" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>150</v>
       </c>
-      <c r="U83" s="24">
+      <c r="U83" s="6">
         <f>VLOOKUP(A83,[1]Sheet!$A:$T,20,0)</f>
         <v>150</v>
       </c>
-      <c r="V83" s="24"/>
+      <c r="V83" s="6"/>
       <c r="W83" s="6">
+        <f t="shared" si="24"/>
+        <v>64.81481481481481</v>
+      </c>
+      <c r="X83" s="6">
         <f t="shared" si="23"/>
-        <v>64.81481481481481</v>
-      </c>
-      <c r="X83" s="6">
-        <f t="shared" si="22"/>
         <v>37.037037037037038</v>
       </c>
       <c r="Y83" s="6">
@@ -15081,10 +15305,13 @@
         <v>38</v>
       </c>
       <c r="AJ83" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>22.5</v>
       </c>
-      <c r="AK83" s="6"/>
+      <c r="AK83" s="6">
+        <f t="shared" si="26"/>
+        <v>0.81</v>
+      </c>
       <c r="AL83" s="6"/>
       <c r="AM83" s="6"/>
       <c r="AN83" s="6"/>
@@ -15131,7 +15358,7 @@
         <v>29</v>
       </c>
       <c r="L84" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-4</v>
       </c>
       <c r="M84" s="6"/>
@@ -15144,25 +15371,25 @@
         <v>150</v>
       </c>
       <c r="R84" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5</v>
       </c>
       <c r="S84" s="4"/>
       <c r="T84" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>100</v>
       </c>
-      <c r="U84" s="24">
+      <c r="U84" s="6">
         <f>VLOOKUP(A84,[1]Sheet!$A:$T,20,0)</f>
         <v>100</v>
       </c>
-      <c r="V84" s="24"/>
+      <c r="V84" s="6"/>
       <c r="W84" s="6">
+        <f t="shared" si="24"/>
+        <v>51.6</v>
+      </c>
+      <c r="X84" s="6">
         <f t="shared" si="23"/>
-        <v>51.6</v>
-      </c>
-      <c r="X84" s="6">
-        <f t="shared" si="22"/>
         <v>31.6</v>
       </c>
       <c r="Y84" s="6">
@@ -15199,10 +15426,13 @@
         <v>38</v>
       </c>
       <c r="AJ84" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>15</v>
       </c>
-      <c r="AK84" s="6"/>
+      <c r="AK84" s="6">
+        <f t="shared" si="26"/>
+        <v>0.75</v>
+      </c>
       <c r="AL84" s="6"/>
       <c r="AM84" s="6"/>
       <c r="AN84" s="6"/>
@@ -15251,7 +15481,7 @@
         <v>97</v>
       </c>
       <c r="L85" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-12</v>
       </c>
       <c r="M85" s="6"/>
@@ -15262,28 +15492,28 @@
       <c r="P85" s="6"/>
       <c r="Q85" s="6"/>
       <c r="R85" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>17</v>
       </c>
       <c r="S85" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>52</v>
       </c>
       <c r="T85" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>80</v>
       </c>
-      <c r="U85" s="24">
+      <c r="U85" s="6">
         <f>VLOOKUP(A85,[1]Sheet!$A:$T,20,0)</f>
         <v>80</v>
       </c>
-      <c r="V85" s="24"/>
+      <c r="V85" s="6"/>
       <c r="W85" s="6">
+        <f t="shared" si="24"/>
+        <v>16.647058823529413</v>
+      </c>
+      <c r="X85" s="6">
         <f t="shared" si="23"/>
-        <v>16.647058823529413</v>
-      </c>
-      <c r="X85" s="6">
-        <f t="shared" si="22"/>
         <v>11.941176470588236</v>
       </c>
       <c r="Y85" s="6">
@@ -15318,10 +15548,13 @@
       </c>
       <c r="AI85" s="6"/>
       <c r="AJ85" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>26.400000000000002</v>
       </c>
-      <c r="AK85" s="6"/>
+      <c r="AK85" s="6">
+        <f t="shared" si="26"/>
+        <v>5.61</v>
+      </c>
       <c r="AL85" s="6"/>
       <c r="AM85" s="6"/>
       <c r="AN85" s="6"/>
@@ -15370,7 +15603,7 @@
         <v>267</v>
       </c>
       <c r="L86" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-12</v>
       </c>
       <c r="M86" s="6"/>
@@ -15381,28 +15614,28 @@
       <c r="P86" s="6"/>
       <c r="Q86" s="6"/>
       <c r="R86" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>51</v>
       </c>
       <c r="S86" s="4">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>370</v>
       </c>
       <c r="T86" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>460</v>
       </c>
-      <c r="U86" s="24">
+      <c r="U86" s="6">
         <f>VLOOKUP(A86,[1]Sheet!$A:$T,20,0)</f>
         <v>460</v>
       </c>
-      <c r="V86" s="24"/>
+      <c r="V86" s="6"/>
       <c r="W86" s="6">
+        <f t="shared" si="24"/>
+        <v>16.764705882352942</v>
+      </c>
+      <c r="X86" s="6">
         <f t="shared" si="23"/>
-        <v>16.764705882352942</v>
-      </c>
-      <c r="X86" s="6">
-        <f t="shared" si="22"/>
         <v>7.7450980392156863</v>
       </c>
       <c r="Y86" s="6">
@@ -15439,10 +15672,13 @@
         <v>38</v>
       </c>
       <c r="AJ86" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>69</v>
       </c>
-      <c r="AK86" s="6"/>
+      <c r="AK86" s="6">
+        <f t="shared" si="26"/>
+        <v>7.6499999999999995</v>
+      </c>
       <c r="AL86" s="6"/>
       <c r="AM86" s="6"/>
       <c r="AN86" s="6"/>
@@ -15459,95 +15695,98 @@
       <c r="AY86" s="6"/>
     </row>
     <row r="87" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C87" s="11"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
-      <c r="G87" s="12">
+      <c r="C87" s="10"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="11">
         <v>0</v>
       </c>
-      <c r="H87" s="11">
+      <c r="H87" s="10">
         <v>45</v>
       </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J87" s="11"/>
-      <c r="K87" s="11"/>
-      <c r="L87" s="11">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="11"/>
-      <c r="N87" s="11"/>
-      <c r="O87" s="11">
-        <v>0</v>
-      </c>
-      <c r="P87" s="11"/>
-      <c r="Q87" s="11"/>
-      <c r="R87" s="11">
+      <c r="J87" s="10"/>
+      <c r="K87" s="10"/>
+      <c r="L87" s="10">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="S87" s="13"/>
+      <c r="M87" s="10"/>
+      <c r="N87" s="10"/>
+      <c r="O87" s="10">
+        <v>0</v>
+      </c>
+      <c r="P87" s="10"/>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S87" s="12"/>
       <c r="T87" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U87" s="6"/>
+      <c r="V87" s="6"/>
+      <c r="W87" s="6" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X87" s="10" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y87" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ87" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U87" s="24"/>
-      <c r="V87" s="24"/>
-      <c r="W87" s="6" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X87" s="11" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y87" s="11">
+      <c r="AK87" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH87" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI87" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ87" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK87" s="6"/>
       <c r="AL87" s="6"/>
       <c r="AM87" s="6"/>
       <c r="AN87" s="6"/>
@@ -15564,103 +15803,106 @@
       <c r="AY87" s="6"/>
     </row>
     <row r="88" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C88" s="11"/>
-      <c r="D88" s="11">
+      <c r="C88" s="10"/>
+      <c r="D88" s="10">
         <v>6.6580000000000004</v>
       </c>
-      <c r="E88" s="11">
+      <c r="E88" s="10">
         <v>6.6609999999999996</v>
       </c>
-      <c r="F88" s="11">
+      <c r="F88" s="10">
         <v>-3.0000000000000001E-3</v>
       </c>
-      <c r="G88" s="12">
+      <c r="G88" s="11">
         <v>0</v>
       </c>
-      <c r="H88" s="11">
+      <c r="H88" s="10">
         <v>30</v>
       </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J88" s="11"/>
-      <c r="K88" s="11">
+      <c r="J88" s="10"/>
+      <c r="K88" s="10">
         <v>9.5500000000000007</v>
       </c>
-      <c r="L88" s="11">
-        <f t="shared" si="20"/>
+      <c r="L88" s="10">
+        <f t="shared" si="21"/>
         <v>-2.8890000000000011</v>
       </c>
-      <c r="M88" s="11"/>
-      <c r="N88" s="11"/>
-      <c r="O88" s="11">
+      <c r="M88" s="10"/>
+      <c r="N88" s="10"/>
+      <c r="O88" s="10">
         <v>0</v>
       </c>
-      <c r="P88" s="11"/>
-      <c r="Q88" s="11"/>
-      <c r="R88" s="11">
-        <f t="shared" si="21"/>
+      <c r="P88" s="10"/>
+      <c r="Q88" s="10"/>
+      <c r="R88" s="10">
+        <f t="shared" si="22"/>
         <v>1.3321999999999998</v>
       </c>
-      <c r="S88" s="13"/>
+      <c r="S88" s="12"/>
       <c r="T88" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U88" s="6"/>
+      <c r="V88" s="6"/>
+      <c r="W88" s="6">
+        <f t="shared" si="24"/>
+        <v>-2.2519141270079569E-3</v>
+      </c>
+      <c r="X88" s="10">
+        <f t="shared" si="23"/>
+        <v>-2.2519141270079569E-3</v>
+      </c>
+      <c r="Y88" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ88" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U88" s="24"/>
-      <c r="V88" s="24"/>
-      <c r="W88" s="6">
-        <f t="shared" si="23"/>
-        <v>-2.2519141270079569E-3</v>
-      </c>
-      <c r="X88" s="11">
-        <f t="shared" si="22"/>
-        <v>-2.2519141270079569E-3</v>
-      </c>
-      <c r="Y88" s="11">
+      <c r="AK88" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH88" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI88" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ88" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK88" s="6"/>
       <c r="AL88" s="6"/>
       <c r="AM88" s="6"/>
       <c r="AN88" s="6"/>
@@ -15677,95 +15919,98 @@
       <c r="AY88" s="6"/>
     </row>
     <row r="89" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="12">
+      <c r="C89" s="10"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="11">
         <v>0</v>
       </c>
-      <c r="H89" s="11">
+      <c r="H89" s="10">
         <v>45</v>
       </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J89" s="11"/>
-      <c r="K89" s="11"/>
-      <c r="L89" s="11">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="M89" s="11"/>
-      <c r="N89" s="11"/>
-      <c r="O89" s="11">
-        <v>0</v>
-      </c>
-      <c r="P89" s="11"/>
-      <c r="Q89" s="11"/>
-      <c r="R89" s="11">
+      <c r="J89" s="10"/>
+      <c r="K89" s="10"/>
+      <c r="L89" s="10">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="S89" s="13"/>
+      <c r="M89" s="10"/>
+      <c r="N89" s="10"/>
+      <c r="O89" s="10">
+        <v>0</v>
+      </c>
+      <c r="P89" s="10"/>
+      <c r="Q89" s="10"/>
+      <c r="R89" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S89" s="12"/>
       <c r="T89" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U89" s="6"/>
+      <c r="V89" s="6"/>
+      <c r="W89" s="6" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X89" s="10" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y89" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ89" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U89" s="24"/>
-      <c r="V89" s="24"/>
-      <c r="W89" s="6" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X89" s="11" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y89" s="11">
+      <c r="AK89" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH89" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI89" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ89" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK89" s="6"/>
       <c r="AL89" s="6"/>
       <c r="AM89" s="6"/>
       <c r="AN89" s="6"/>
@@ -15782,103 +16027,106 @@
       <c r="AY89" s="6"/>
     </row>
     <row r="90" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C90" s="11"/>
-      <c r="D90" s="11">
+      <c r="C90" s="10"/>
+      <c r="D90" s="10">
         <v>8.7129999999999992</v>
       </c>
-      <c r="E90" s="11">
+      <c r="E90" s="10">
         <v>4.3159999999999998</v>
       </c>
-      <c r="F90" s="11">
+      <c r="F90" s="10">
         <v>3.0139999999999998</v>
       </c>
-      <c r="G90" s="12">
+      <c r="G90" s="11">
         <v>0</v>
       </c>
-      <c r="H90" s="11">
+      <c r="H90" s="10">
         <v>30</v>
       </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J90" s="11"/>
-      <c r="K90" s="11">
+      <c r="J90" s="10"/>
+      <c r="K90" s="10">
         <v>4.5</v>
       </c>
-      <c r="L90" s="11">
-        <f t="shared" si="20"/>
+      <c r="L90" s="10">
+        <f t="shared" si="21"/>
         <v>-0.18400000000000016</v>
       </c>
-      <c r="M90" s="11"/>
-      <c r="N90" s="11"/>
-      <c r="O90" s="11">
+      <c r="M90" s="10"/>
+      <c r="N90" s="10"/>
+      <c r="O90" s="10">
         <v>0</v>
       </c>
-      <c r="P90" s="11"/>
-      <c r="Q90" s="11"/>
-      <c r="R90" s="11">
-        <f t="shared" si="21"/>
+      <c r="P90" s="10"/>
+      <c r="Q90" s="10"/>
+      <c r="R90" s="10">
+        <f t="shared" si="22"/>
         <v>0.86319999999999997</v>
       </c>
-      <c r="S90" s="13"/>
+      <c r="S90" s="12"/>
       <c r="T90" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U90" s="6"/>
+      <c r="V90" s="6"/>
+      <c r="W90" s="6">
+        <f t="shared" si="24"/>
+        <v>3.4916589434661724</v>
+      </c>
+      <c r="X90" s="10">
+        <f t="shared" si="23"/>
+        <v>3.4916589434661724</v>
+      </c>
+      <c r="Y90" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI90" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ90" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U90" s="24"/>
-      <c r="V90" s="24"/>
-      <c r="W90" s="6">
-        <f t="shared" si="23"/>
-        <v>3.4916589434661724</v>
-      </c>
-      <c r="X90" s="11">
-        <f t="shared" si="22"/>
-        <v>3.4916589434661724</v>
-      </c>
-      <c r="Y90" s="11">
+      <c r="AK90" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH90" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI90" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ90" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK90" s="6"/>
       <c r="AL90" s="6"/>
       <c r="AM90" s="6"/>
       <c r="AN90" s="6"/>
@@ -15927,7 +16175,7 @@
         <v>168</v>
       </c>
       <c r="L91" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="M91" s="6"/>
@@ -15938,7 +16186,7 @@
       <c r="P91" s="6"/>
       <c r="Q91" s="6"/>
       <c r="R91" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>34</v>
       </c>
       <c r="S91" s="4">
@@ -15949,17 +16197,17 @@
         <f>U91</f>
         <v>300</v>
       </c>
-      <c r="U91" s="24">
+      <c r="U91" s="6">
         <f>VLOOKUP(A91,[1]Sheet!$A:$T,20,0)</f>
         <v>300</v>
       </c>
-      <c r="V91" s="24"/>
+      <c r="V91" s="6"/>
       <c r="W91" s="6">
+        <f t="shared" si="24"/>
+        <v>13.294117647058824</v>
+      </c>
+      <c r="X91" s="6">
         <f t="shared" si="23"/>
-        <v>13.294117647058824</v>
-      </c>
-      <c r="X91" s="6">
-        <f t="shared" si="22"/>
         <v>4.4705882352941178</v>
       </c>
       <c r="Y91" s="6">
@@ -15996,10 +16244,13 @@
         <v>50</v>
       </c>
       <c r="AJ91" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>120</v>
       </c>
-      <c r="AK91" s="6"/>
+      <c r="AK91" s="6">
+        <f t="shared" si="26"/>
+        <v>13.600000000000001</v>
+      </c>
       <c r="AL91" s="6"/>
       <c r="AM91" s="6"/>
       <c r="AN91" s="6"/>
@@ -16016,99 +16267,102 @@
       <c r="AY91" s="6"/>
     </row>
     <row r="92" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="10">
         <v>2</v>
       </c>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="12">
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="11">
         <v>0</v>
       </c>
-      <c r="H92" s="11">
+      <c r="H92" s="10">
         <v>60</v>
       </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J92" s="11"/>
-      <c r="K92" s="11">
+      <c r="J92" s="10"/>
+      <c r="K92" s="10">
         <v>8</v>
       </c>
-      <c r="L92" s="11">
-        <f t="shared" si="20"/>
+      <c r="L92" s="10">
+        <f t="shared" si="21"/>
         <v>-8</v>
       </c>
-      <c r="M92" s="11"/>
-      <c r="N92" s="11"/>
-      <c r="O92" s="11">
+      <c r="M92" s="10"/>
+      <c r="N92" s="10"/>
+      <c r="O92" s="10">
         <v>0</v>
       </c>
-      <c r="P92" s="11"/>
-      <c r="Q92" s="11"/>
-      <c r="R92" s="11">
-        <f t="shared" si="21"/>
+      <c r="P92" s="10"/>
+      <c r="Q92" s="10"/>
+      <c r="R92" s="10">
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="S92" s="13"/>
+      <c r="S92" s="12"/>
       <c r="T92" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U92" s="6"/>
+      <c r="V92" s="6"/>
+      <c r="W92" s="6" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X92" s="10" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y92" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="Z92" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AA92" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="AB92" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="AC92" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="AD92" s="10">
+        <v>2</v>
+      </c>
+      <c r="AE92" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="AF92" s="10">
+        <v>4.2</v>
+      </c>
+      <c r="AG92" s="10">
+        <v>8.6</v>
+      </c>
+      <c r="AH92" s="10">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AI92" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ92" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U92" s="24"/>
-      <c r="V92" s="24"/>
-      <c r="W92" s="6" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X92" s="11" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y92" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="Z92" s="11">
-        <v>0.4</v>
-      </c>
-      <c r="AA92" s="11">
-        <v>1.6</v>
-      </c>
-      <c r="AB92" s="11">
-        <v>2.4</v>
-      </c>
-      <c r="AC92" s="11">
-        <v>2.8</v>
-      </c>
-      <c r="AD92" s="11">
-        <v>2</v>
-      </c>
-      <c r="AE92" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="AF92" s="11">
-        <v>4.2</v>
-      </c>
-      <c r="AG92" s="11">
-        <v>8.6</v>
-      </c>
-      <c r="AH92" s="11">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="AI92" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ92" s="6">
-        <f t="shared" si="24"/>
+      <c r="AK92" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AK92" s="6"/>
       <c r="AL92" s="6"/>
       <c r="AM92" s="6"/>
       <c r="AN92" s="6"/>
@@ -16125,95 +16379,98 @@
       <c r="AY92" s="6"/>
     </row>
     <row r="93" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="12">
+      <c r="C93" s="10"/>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10"/>
+      <c r="F93" s="10"/>
+      <c r="G93" s="11">
         <v>0</v>
       </c>
-      <c r="H93" s="11">
+      <c r="H93" s="10">
         <v>45</v>
       </c>
-      <c r="I93" s="11" t="s">
+      <c r="I93" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J93" s="11"/>
-      <c r="K93" s="11"/>
-      <c r="L93" s="11">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="M93" s="11"/>
-      <c r="N93" s="11"/>
-      <c r="O93" s="11">
-        <v>0</v>
-      </c>
-      <c r="P93" s="11"/>
-      <c r="Q93" s="11"/>
-      <c r="R93" s="11">
+      <c r="J93" s="10"/>
+      <c r="K93" s="10"/>
+      <c r="L93" s="10">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="S93" s="13"/>
+      <c r="M93" s="10"/>
+      <c r="N93" s="10"/>
+      <c r="O93" s="10">
+        <v>0</v>
+      </c>
+      <c r="P93" s="10"/>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="S93" s="12"/>
       <c r="T93" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U93" s="6"/>
+      <c r="V93" s="6"/>
+      <c r="W93" s="6" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X93" s="10" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y93" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ93" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U93" s="24"/>
-      <c r="V93" s="24"/>
-      <c r="W93" s="6" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X93" s="11" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y93" s="11">
+      <c r="AK93" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH93" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI93" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ93" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK93" s="6"/>
       <c r="AL93" s="6"/>
       <c r="AM93" s="6"/>
       <c r="AN93" s="6"/>
@@ -16230,95 +16487,98 @@
       <c r="AY93" s="6"/>
     </row>
     <row r="94" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C94" s="11"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="12">
+      <c r="C94" s="10"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="11">
         <v>0</v>
       </c>
-      <c r="H94" s="11"/>
-      <c r="I94" s="11" t="s">
+      <c r="H94" s="10"/>
+      <c r="I94" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J94" s="11"/>
-      <c r="K94" s="11">
+      <c r="J94" s="10"/>
+      <c r="K94" s="10">
         <v>3</v>
       </c>
-      <c r="L94" s="11">
-        <f t="shared" si="20"/>
+      <c r="L94" s="10">
+        <f t="shared" si="21"/>
         <v>-3</v>
       </c>
-      <c r="M94" s="11"/>
-      <c r="N94" s="11"/>
-      <c r="O94" s="11">
+      <c r="M94" s="10"/>
+      <c r="N94" s="10"/>
+      <c r="O94" s="10">
         <v>0</v>
       </c>
-      <c r="P94" s="11"/>
-      <c r="Q94" s="11"/>
-      <c r="R94" s="11">
-        <f t="shared" si="21"/>
+      <c r="P94" s="10"/>
+      <c r="Q94" s="10"/>
+      <c r="R94" s="10">
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="S94" s="13"/>
+      <c r="S94" s="12"/>
       <c r="T94" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U94" s="6"/>
+      <c r="V94" s="6"/>
+      <c r="W94" s="6" t="e">
+        <f t="shared" si="24"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X94" s="10" t="e">
+        <f t="shared" si="23"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y94" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ94" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U94" s="24"/>
-      <c r="V94" s="24"/>
-      <c r="W94" s="6" t="e">
-        <f t="shared" si="23"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X94" s="11" t="e">
-        <f t="shared" si="22"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y94" s="11">
+      <c r="AK94" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH94" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI94" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ94" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK94" s="6"/>
       <c r="AL94" s="6"/>
       <c r="AM94" s="6"/>
       <c r="AN94" s="6"/>
@@ -16365,7 +16625,7 @@
         <v>50</v>
       </c>
       <c r="L95" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-6</v>
       </c>
       <c r="M95" s="6"/>
@@ -16376,65 +16636,68 @@
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
       <c r="R95" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>8.8000000000000007</v>
       </c>
       <c r="S95" s="4"/>
       <c r="T95" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U95" s="6">
+        <f>VLOOKUP(A95,[1]Sheet!$A:$T,20,0)</f>
+        <v>20</v>
+      </c>
+      <c r="V95" s="6"/>
+      <c r="W95" s="6">
+        <f t="shared" si="24"/>
+        <v>19.43181818181818</v>
+      </c>
+      <c r="X95" s="6">
+        <f t="shared" si="23"/>
+        <v>19.43181818181818</v>
+      </c>
+      <c r="Y95" s="6">
+        <v>15.2</v>
+      </c>
+      <c r="Z95" s="6">
+        <v>10.4</v>
+      </c>
+      <c r="AA95" s="6">
+        <v>19.8</v>
+      </c>
+      <c r="AB95" s="6">
+        <v>18</v>
+      </c>
+      <c r="AC95" s="6">
+        <v>14.6</v>
+      </c>
+      <c r="AD95" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE95" s="6">
+        <v>15.6</v>
+      </c>
+      <c r="AF95" s="6">
+        <v>10.8</v>
+      </c>
+      <c r="AG95" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH95" s="6">
+        <v>12</v>
+      </c>
+      <c r="AI95" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ95" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U95" s="24">
-        <f>VLOOKUP(A95,[1]Sheet!$A:$T,20,0)</f>
-        <v>20</v>
-      </c>
-      <c r="V95" s="24"/>
-      <c r="W95" s="6">
-        <f t="shared" si="23"/>
-        <v>19.43181818181818</v>
-      </c>
-      <c r="X95" s="6">
-        <f t="shared" si="22"/>
-        <v>19.43181818181818</v>
-      </c>
-      <c r="Y95" s="6">
-        <v>15.2</v>
-      </c>
-      <c r="Z95" s="6">
-        <v>10.4</v>
-      </c>
-      <c r="AA95" s="6">
-        <v>19.8</v>
-      </c>
-      <c r="AB95" s="6">
-        <v>18</v>
-      </c>
-      <c r="AC95" s="6">
-        <v>14.6</v>
-      </c>
-      <c r="AD95" s="6">
-        <v>12</v>
-      </c>
-      <c r="AE95" s="6">
-        <v>15.6</v>
-      </c>
-      <c r="AF95" s="6">
-        <v>10.8</v>
-      </c>
-      <c r="AG95" s="6">
-        <v>2</v>
-      </c>
-      <c r="AH95" s="6">
-        <v>12</v>
-      </c>
-      <c r="AI95" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ95" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK95" s="6"/>
+      <c r="AK95" s="6">
+        <f t="shared" si="26"/>
+        <v>2.9040000000000004</v>
+      </c>
       <c r="AL95" s="6"/>
       <c r="AM95" s="6"/>
       <c r="AN95" s="6"/>
@@ -16451,103 +16714,106 @@
       <c r="AY95" s="6"/>
     </row>
     <row r="96" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C96" s="11">
+      <c r="C96" s="10">
         <v>86</v>
       </c>
-      <c r="D96" s="11"/>
-      <c r="E96" s="11">
+      <c r="D96" s="10"/>
+      <c r="E96" s="10">
         <v>45</v>
       </c>
-      <c r="F96" s="11">
+      <c r="F96" s="10">
         <v>39</v>
       </c>
-      <c r="G96" s="12">
+      <c r="G96" s="11">
         <v>0</v>
       </c>
-      <c r="H96" s="11">
+      <c r="H96" s="10">
         <v>60</v>
       </c>
-      <c r="I96" s="11" t="s">
+      <c r="I96" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="J96" s="11"/>
-      <c r="K96" s="11">
+      <c r="J96" s="10"/>
+      <c r="K96" s="10">
         <v>45</v>
       </c>
-      <c r="L96" s="11">
-        <f t="shared" si="20"/>
+      <c r="L96" s="10">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="M96" s="11"/>
-      <c r="N96" s="11"/>
-      <c r="O96" s="11">
+      <c r="M96" s="10"/>
+      <c r="N96" s="10"/>
+      <c r="O96" s="10">
         <v>0</v>
       </c>
-      <c r="P96" s="11"/>
-      <c r="Q96" s="11"/>
-      <c r="R96" s="11">
-        <f t="shared" si="21"/>
+      <c r="P96" s="10"/>
+      <c r="Q96" s="10"/>
+      <c r="R96" s="10">
+        <f t="shared" si="22"/>
         <v>9</v>
       </c>
-      <c r="S96" s="13"/>
+      <c r="S96" s="12"/>
       <c r="T96" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U96" s="6"/>
+      <c r="V96" s="6"/>
+      <c r="W96" s="6">
+        <f t="shared" si="24"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="X96" s="10">
+        <f t="shared" si="23"/>
+        <v>4.333333333333333</v>
+      </c>
+      <c r="Y96" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="Z96" s="10">
+        <v>4.8</v>
+      </c>
+      <c r="AA96" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="AB96" s="10">
+        <v>1.4</v>
+      </c>
+      <c r="AC96" s="10">
+        <v>8.4</v>
+      </c>
+      <c r="AD96" s="10">
+        <v>3.6</v>
+      </c>
+      <c r="AE96" s="10">
+        <v>6.4</v>
+      </c>
+      <c r="AF96" s="10">
+        <v>6.4</v>
+      </c>
+      <c r="AG96" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="AH96" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ96" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U96" s="24"/>
-      <c r="V96" s="24"/>
-      <c r="W96" s="6">
-        <f t="shared" si="23"/>
-        <v>4.333333333333333</v>
-      </c>
-      <c r="X96" s="11">
-        <f t="shared" si="22"/>
-        <v>4.333333333333333</v>
-      </c>
-      <c r="Y96" s="11">
-        <v>1.6</v>
-      </c>
-      <c r="Z96" s="11">
-        <v>4.8</v>
-      </c>
-      <c r="AA96" s="11">
-        <v>7.4</v>
-      </c>
-      <c r="AB96" s="11">
-        <v>1.4</v>
-      </c>
-      <c r="AC96" s="11">
-        <v>8.4</v>
-      </c>
-      <c r="AD96" s="11">
-        <v>3.6</v>
-      </c>
-      <c r="AE96" s="11">
-        <v>6.4</v>
-      </c>
-      <c r="AF96" s="11">
-        <v>6.4</v>
-      </c>
-      <c r="AG96" s="11">
-        <v>5.2</v>
-      </c>
-      <c r="AH96" s="11">
+      <c r="AK96" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="AI96" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ96" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK96" s="6"/>
       <c r="AL96" s="6"/>
       <c r="AM96" s="6"/>
       <c r="AN96" s="6"/>
@@ -16596,7 +16862,7 @@
         <v>356</v>
       </c>
       <c r="L97" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="M97" s="6"/>
@@ -16607,7 +16873,7 @@
       <c r="P97" s="6"/>
       <c r="Q97" s="6"/>
       <c r="R97" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>70.8</v>
       </c>
       <c r="S97" s="4">
@@ -16615,20 +16881,20 @@
         <v>550.19999999999993</v>
       </c>
       <c r="T97" s="4">
-        <f t="shared" ref="T97" si="28">U97</f>
+        <f t="shared" ref="T97" si="30">U97</f>
         <v>800</v>
       </c>
-      <c r="U97" s="24">
+      <c r="U97" s="6">
         <f>VLOOKUP(A97,[1]Sheet!$A:$T,20,0)</f>
         <v>800</v>
       </c>
-      <c r="V97" s="24"/>
+      <c r="V97" s="6"/>
       <c r="W97" s="6">
+        <f t="shared" si="24"/>
+        <v>17.528248587570623</v>
+      </c>
+      <c r="X97" s="6">
         <f t="shared" si="23"/>
-        <v>17.528248587570623</v>
-      </c>
-      <c r="X97" s="6">
-        <f t="shared" si="22"/>
         <v>6.2288135593220337</v>
       </c>
       <c r="Y97" s="6">
@@ -16663,10 +16929,13 @@
       </c>
       <c r="AI97" s="6"/>
       <c r="AJ97" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>80</v>
       </c>
-      <c r="AK97" s="6"/>
+      <c r="AK97" s="6">
+        <f t="shared" si="26"/>
+        <v>7.08</v>
+      </c>
       <c r="AL97" s="6"/>
       <c r="AM97" s="6"/>
       <c r="AN97" s="6"/>
@@ -16715,7 +16984,7 @@
         <v>275</v>
       </c>
       <c r="L98" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="M98" s="6"/>
@@ -16726,27 +16995,27 @@
       <c r="P98" s="6"/>
       <c r="Q98" s="6"/>
       <c r="R98" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>56</v>
       </c>
       <c r="S98" s="4">
-        <f t="shared" ref="S98:S101" si="29">15*R98-Q98-P98-O98-F98</f>
+        <f t="shared" ref="S98:S101" si="31">15*R98-Q98-P98-O98-F98</f>
         <v>203</v>
       </c>
       <c r="T98" s="4">
         <v>450</v>
       </c>
-      <c r="U98" s="24">
+      <c r="U98" s="6">
         <f>VLOOKUP(A98,[1]Sheet!$A:$T,20,0)</f>
         <v>500</v>
       </c>
-      <c r="V98" s="24"/>
+      <c r="V98" s="6"/>
       <c r="W98" s="6">
+        <f t="shared" si="24"/>
+        <v>19.410714285714285</v>
+      </c>
+      <c r="X98" s="6">
         <f t="shared" si="23"/>
-        <v>19.410714285714285</v>
-      </c>
-      <c r="X98" s="6">
-        <f t="shared" si="22"/>
         <v>11.375</v>
       </c>
       <c r="Y98" s="6">
@@ -16781,10 +17050,13 @@
       </c>
       <c r="AI98" s="6"/>
       <c r="AJ98" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>45</v>
       </c>
-      <c r="AK98" s="6"/>
+      <c r="AK98" s="6">
+        <f t="shared" si="26"/>
+        <v>5.6000000000000005</v>
+      </c>
       <c r="AL98" s="6"/>
       <c r="AM98" s="6"/>
       <c r="AN98" s="6"/>
@@ -16833,7 +17105,7 @@
         <v>158</v>
       </c>
       <c r="L99" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-12</v>
       </c>
       <c r="M99" s="6"/>
@@ -16844,27 +17116,27 @@
       <c r="P99" s="6"/>
       <c r="Q99" s="6"/>
       <c r="R99" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>29.2</v>
       </c>
       <c r="S99" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>106</v>
       </c>
       <c r="T99" s="4">
         <v>220</v>
       </c>
-      <c r="U99" s="24">
+      <c r="U99" s="6">
         <f>VLOOKUP(A99,[1]Sheet!$A:$T,20,0)</f>
         <v>280</v>
       </c>
-      <c r="V99" s="24"/>
+      <c r="V99" s="6"/>
       <c r="W99" s="6">
+        <f t="shared" si="24"/>
+        <v>18.904109589041095</v>
+      </c>
+      <c r="X99" s="6">
         <f t="shared" si="23"/>
-        <v>18.904109589041095</v>
-      </c>
-      <c r="X99" s="6">
-        <f t="shared" si="22"/>
         <v>11.36986301369863</v>
       </c>
       <c r="Y99" s="6">
@@ -16901,10 +17173,13 @@
         <v>147</v>
       </c>
       <c r="AJ99" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>88</v>
       </c>
-      <c r="AK99" s="6"/>
+      <c r="AK99" s="6">
+        <f t="shared" si="26"/>
+        <v>11.68</v>
+      </c>
       <c r="AL99" s="6"/>
       <c r="AM99" s="6"/>
       <c r="AN99" s="6"/>
@@ -16951,7 +17226,7 @@
         <v>71</v>
       </c>
       <c r="L100" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-23</v>
       </c>
       <c r="M100" s="6"/>
@@ -16962,25 +17237,25 @@
       <c r="P100" s="6"/>
       <c r="Q100" s="6"/>
       <c r="R100" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>9.6</v>
       </c>
       <c r="S100" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>13</v>
       </c>
       <c r="T100" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>13</v>
       </c>
-      <c r="U100" s="24"/>
-      <c r="V100" s="24"/>
+      <c r="U100" s="6"/>
+      <c r="V100" s="6"/>
       <c r="W100" s="6">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="X100" s="6">
         <f t="shared" si="23"/>
-        <v>15</v>
-      </c>
-      <c r="X100" s="6">
-        <f t="shared" si="22"/>
         <v>13.645833333333334</v>
       </c>
       <c r="Y100" s="6">
@@ -17015,10 +17290,13 @@
       </c>
       <c r="AI100" s="6"/>
       <c r="AJ100" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1.3</v>
       </c>
-      <c r="AK100" s="6"/>
+      <c r="AK100" s="6">
+        <f t="shared" si="26"/>
+        <v>0.96</v>
+      </c>
       <c r="AL100" s="6"/>
       <c r="AM100" s="6"/>
       <c r="AN100" s="6"/>
@@ -17065,7 +17343,7 @@
         <v>77</v>
       </c>
       <c r="L101" s="6">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-14</v>
       </c>
       <c r="M101" s="6"/>
@@ -17076,25 +17354,25 @@
       <c r="P101" s="6"/>
       <c r="Q101" s="6"/>
       <c r="R101" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>12.6</v>
       </c>
       <c r="S101" s="4">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7</v>
       </c>
       <c r="T101" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>7</v>
       </c>
-      <c r="U101" s="24"/>
-      <c r="V101" s="24"/>
+      <c r="U101" s="6"/>
+      <c r="V101" s="6"/>
       <c r="W101" s="6">
+        <f t="shared" si="24"/>
+        <v>15</v>
+      </c>
+      <c r="X101" s="6">
         <f t="shared" si="23"/>
-        <v>15</v>
-      </c>
-      <c r="X101" s="6">
-        <f t="shared" si="22"/>
         <v>14.444444444444445</v>
       </c>
       <c r="Y101" s="6">
@@ -17129,10 +17407,13 @@
       </c>
       <c r="AI101" s="6"/>
       <c r="AJ101" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="AK101" s="6"/>
+      <c r="AK101" s="6">
+        <f t="shared" si="26"/>
+        <v>1.26</v>
+      </c>
       <c r="AL101" s="6"/>
       <c r="AM101" s="6"/>
       <c r="AN101" s="6"/>
@@ -17149,101 +17430,104 @@
       <c r="AY101" s="6"/>
     </row>
     <row r="102" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11">
+      <c r="C102" s="10"/>
+      <c r="D102" s="10">
         <v>40</v>
       </c>
-      <c r="E102" s="11">
+      <c r="E102" s="10">
         <v>40</v>
       </c>
-      <c r="F102" s="11"/>
-      <c r="G102" s="12">
+      <c r="F102" s="10"/>
+      <c r="G102" s="11">
         <v>0</v>
       </c>
-      <c r="H102" s="11">
+      <c r="H102" s="10">
         <v>45</v>
       </c>
-      <c r="I102" s="11" t="s">
+      <c r="I102" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J102" s="11"/>
-      <c r="K102" s="11">
+      <c r="J102" s="10"/>
+      <c r="K102" s="10">
         <v>42</v>
       </c>
-      <c r="L102" s="11">
-        <f t="shared" ref="L102:L104" si="30">E102-K102</f>
+      <c r="L102" s="10">
+        <f t="shared" ref="L102:L104" si="32">E102-K102</f>
         <v>-2</v>
       </c>
-      <c r="M102" s="11"/>
-      <c r="N102" s="11"/>
-      <c r="O102" s="11">
+      <c r="M102" s="10"/>
+      <c r="N102" s="10"/>
+      <c r="O102" s="10">
         <v>0</v>
       </c>
-      <c r="P102" s="11"/>
-      <c r="Q102" s="11"/>
-      <c r="R102" s="11">
-        <f t="shared" si="21"/>
+      <c r="P102" s="10"/>
+      <c r="Q102" s="10"/>
+      <c r="R102" s="10">
+        <f t="shared" si="22"/>
         <v>8</v>
       </c>
-      <c r="S102" s="13"/>
+      <c r="S102" s="12"/>
       <c r="T102" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U102" s="6"/>
+      <c r="V102" s="6"/>
+      <c r="W102" s="6">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="X102" s="10">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Y102" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ102" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U102" s="24"/>
-      <c r="V102" s="24"/>
-      <c r="W102" s="6">
-        <f t="shared" si="23"/>
+      <c r="AK102" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="X102" s="11">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="Y102" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH102" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI102" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="AJ102" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK102" s="6"/>
       <c r="AL102" s="6"/>
       <c r="AM102" s="6"/>
       <c r="AN102" s="6"/>
@@ -17260,99 +17544,102 @@
       <c r="AY102" s="6"/>
     </row>
     <row r="103" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A103" s="11" t="s">
+      <c r="A103" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11">
+      <c r="C103" s="10"/>
+      <c r="D103" s="10">
         <v>1000</v>
       </c>
-      <c r="E103" s="11">
+      <c r="E103" s="10">
         <v>139</v>
       </c>
-      <c r="F103" s="11">
+      <c r="F103" s="10">
         <v>746</v>
       </c>
-      <c r="G103" s="12">
+      <c r="G103" s="11">
         <v>0</v>
       </c>
-      <c r="H103" s="11"/>
-      <c r="I103" s="14" t="s">
+      <c r="H103" s="10"/>
+      <c r="I103" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="J103" s="11"/>
-      <c r="K103" s="11">
+      <c r="J103" s="10"/>
+      <c r="K103" s="10">
         <v>163</v>
       </c>
-      <c r="L103" s="11">
-        <f t="shared" si="30"/>
+      <c r="L103" s="10">
+        <f t="shared" si="32"/>
         <v>-24</v>
       </c>
-      <c r="M103" s="11"/>
-      <c r="N103" s="11"/>
-      <c r="O103" s="11"/>
-      <c r="P103" s="11"/>
-      <c r="Q103" s="11"/>
-      <c r="R103" s="11">
-        <f t="shared" si="21"/>
+      <c r="M103" s="10"/>
+      <c r="N103" s="10"/>
+      <c r="O103" s="10"/>
+      <c r="P103" s="10"/>
+      <c r="Q103" s="10"/>
+      <c r="R103" s="10">
+        <f t="shared" si="22"/>
         <v>27.8</v>
       </c>
-      <c r="S103" s="13"/>
+      <c r="S103" s="12"/>
       <c r="T103" s="4">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="U103" s="6"/>
+      <c r="V103" s="6"/>
+      <c r="W103" s="6">
+        <f t="shared" si="24"/>
+        <v>26.834532374100718</v>
+      </c>
+      <c r="X103" s="10">
+        <f t="shared" si="23"/>
+        <v>26.834532374100718</v>
+      </c>
+      <c r="Y103" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH103" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI103" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="AJ103" s="6">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="U103" s="24"/>
-      <c r="V103" s="24"/>
-      <c r="W103" s="6">
-        <f t="shared" si="23"/>
-        <v>26.834532374100718</v>
-      </c>
-      <c r="X103" s="11">
-        <f t="shared" si="22"/>
-        <v>26.834532374100718</v>
-      </c>
-      <c r="Y103" s="11">
+      <c r="AK103" s="6">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="Z103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AD103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AE103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AF103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AG103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AH103" s="11">
-        <v>0</v>
-      </c>
-      <c r="AI103" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="AJ103" s="6">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
-      <c r="AK103" s="6"/>
       <c r="AL103" s="6"/>
       <c r="AM103" s="6"/>
       <c r="AN103" s="6"/>
@@ -17397,7 +17684,7 @@
         <v>20.95</v>
       </c>
       <c r="L104" s="6">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.10900000000000176</v>
       </c>
       <c r="M104" s="6"/>
@@ -17408,7 +17695,7 @@
       <c r="P104" s="6"/>
       <c r="Q104" s="6"/>
       <c r="R104" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.2118000000000002</v>
       </c>
       <c r="S104" s="4">
@@ -17417,17 +17704,17 @@
       <c r="T104" s="4">
         <v>50</v>
       </c>
-      <c r="U104" s="24">
+      <c r="U104" s="6">
         <f>VLOOKUP(A104,[1]Sheet!$A:$T,20,0)</f>
         <v>70</v>
       </c>
-      <c r="V104" s="24"/>
+      <c r="V104" s="6"/>
       <c r="W104" s="6">
+        <f t="shared" si="24"/>
+        <v>26.405099957262927</v>
+      </c>
+      <c r="X104" s="6">
         <f t="shared" si="23"/>
-        <v>26.405099957262927</v>
-      </c>
-      <c r="X104" s="6">
-        <f t="shared" si="22"/>
         <v>14.533691058454817</v>
       </c>
       <c r="Y104" s="6">
@@ -17464,10 +17751,13 @@
         <v>112</v>
       </c>
       <c r="AJ104" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>50</v>
       </c>
-      <c r="AK104" s="6"/>
+      <c r="AK104" s="6">
+        <f t="shared" si="26"/>
+        <v>4.2118000000000002</v>
+      </c>
       <c r="AL104" s="6"/>
       <c r="AM104" s="6"/>
       <c r="AN104" s="6"/>
